--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-22 23:38 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-03-23 10:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$98.30</t>
+          <t>$99.19</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$98.30</t>
+          <t>$99.19</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $98.30 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $99.19 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$107.12</t>
+          <t>$108.75</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$107.12</t>
+          <t>$108.75</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $107.12 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $108.75 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,486.50</t>
+          <t>$4,265.70</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,486.50</t>
+          <t>$4,265.70</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,486 ▬ (-10.2% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,266 ▬ (-14.6% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.304</t>
+          <t>$5.313</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.304 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.313 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 26.78 ▬. Elevated anxiety; above 20 = fear zone.</t>
+          <t>VIX at 30.11 ▬. Deep fear zone; risk-off sentiment dominant.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>99.54</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>99.54</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 99.54 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 100.10 ▬. Dollar neutral; tracking rate differential.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>9,918</t>
+          <t>9,694</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>9,918</t>
+          <t>9,694</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 9,918 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 9,694 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>53,373</t>
+          <t>51,515</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>53,373</t>
+          <t>51,515</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 53,373 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 51,515 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-03-22 23:38 UTC</t>
+          <t>2026-03-23 10:32 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2075,28 +2075,28 @@
         <v>21647.6113</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>9918.330099999999</v>
+        <v>9694.209999999999</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>53372.5312</v>
+        <v>51515.4883</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>26.78</v>
+        <v>30.11</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>98.3</v>
+        <v>99.19</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>107.12</v>
+        <v>108.75</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4486.5</v>
+        <v>4265.7002</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.304</v>
+        <v>5.3135</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>99.539</v>
+        <v>100.099</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,15 +72,15 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF4D4D"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -181,22 +181,22 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,10 +208,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-23 10:32 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-03-24 10:13 UTC</t>
         </is>
       </c>
     </row>
@@ -709,22 +709,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.88%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.79%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.76%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.79% ▬ (+3bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.88% ▲ (+9bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,32 +751,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.39%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.25%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.26%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.010</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.140</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.25% ▬ (-1bps). Yield within recent range.</t>
+          <t>10Y yield at 4.39% ▲ (+14bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,22 +793,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.96%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.83%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>+0.130</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.83% ▬ (-5bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.96% ▲ (+13bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -840,27 +840,27 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.050</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.51% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -902,7 +902,7 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -986,7 +986,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1070,7 +1070,7 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1203,7 +1203,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$99.19</t>
+          <t>$90.54</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$99.19</t>
+          <t>$90.54</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,7 +1240,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $99.19 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $90.54 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$108.75</t>
+          <t>$101.59</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$108.75</t>
+          <t>$101.59</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $108.75 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $101.59 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,265.70</t>
+          <t>$4,421.10</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,265.70</t>
+          <t>$4,421.10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,7 +1324,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,266 ▬ (-14.6% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,421 ▬ (-11.6% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.313</t>
+          <t>$5.395</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.313 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.395 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>88bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>90bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>91bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>-2.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1420,14 +1420,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 90bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 88bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,32 +1444,32 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>324bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>327bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>320bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+7.000</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+          <t>-3.000</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 327bps ▲. Moderate risk premium.</t>
+          <t>HY spread at 324bps ▬. Moderate risk premium.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 30.11 ▬. Deep fear zone; risk-off sentiment dominant.</t>
+          <t>VIX at 26.25 ▬. Elevated anxiety; above 20 = fear zone.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>99.32</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>99.32</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 100.10 ▬. Dollar neutral; tracking rate differential.</t>
+          <t>DXY at 99.32 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,506</t>
+          <t>6,581</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,506</t>
+          <t>6,581</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,506 ▬. Below 200-day SMA (6,622) — trend broken. -6.8% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,581 ▬. Below 200-day SMA (6,625) — trend broken. -5.7% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>45,577</t>
+          <t>46,208</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>45,577</t>
+          <t>46,208</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,7 +1674,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 45,577 ▬.</t>
+          <t>Dow Jones at 46,208 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>21,648</t>
+          <t>21,947</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>21,648</t>
+          <t>21,947</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 21,648 ▬. Below 200-day SMA — tech trend under pressure.</t>
+          <t>Nasdaq at 21,947 ▬. Below 200-day SMA — tech trend under pressure.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>9,694</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>9,694</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 9,694 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 9,904 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>51,515</t>
+          <t>52,252</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>51,515</t>
+          <t>52,252</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 51,515 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 52,252 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,20 +2019,20 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-03-23 10:32 UTC</t>
+          <t>2026-03-24 10:13 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.79</v>
+        <v>3.88</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.25</v>
+        <v>4.39</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.83</v>
+        <v>4.96</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>0.51</v>
@@ -2060,43 +2060,43 @@
         <v>56.4</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6506.48</v>
+        <v>6581</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>45577.4688</v>
+        <v>46208.4688</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>21647.6113</v>
+        <v>21946.7598</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>9694.209999999999</v>
+        <v>9904.169900000001</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>51515.4883</v>
+        <v>52252.2812</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>30.11</v>
+        <v>26.25</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>99.19</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>108.75</v>
+        <v>101.59</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4265.7002</v>
+        <v>4421.1001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.3135</v>
+        <v>5.395</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>100.099</v>
+        <v>99.321</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,9 +72,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -83,14 +84,13 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -181,10 +181,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,22 +193,19 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -606,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-24 10:13 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-03-25 10:13 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +706,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.83%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.88%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.090</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>▬</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.88% ▲ (+9bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.83% ▬ (-5bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,32 +748,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.39%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.25%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.140</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.39% ▲ (+14bps). Yield within recent range.</t>
+          <t>10Y yield at 4.34% ▬ (-5bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,32 +790,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.96%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.83%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.130</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.96% ▲ (+13bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.91% ▬ (-5bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +832,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.51%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.49% ▼. Flat curve; economic uncertainty persists.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,12 +894,12 @@
           <t>+0.100</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -939,12 +936,12 @@
           <t>-8000.000</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +978,12 @@
           <t>-218.000</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1023,12 +1020,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1065,12 +1062,12 @@
           <t>+3.500</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,7 +1111,7 @@
           <t>-0.164</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1156,12 +1153,12 @@
           <t>-0.216</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1203,7 +1200,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$90.54</t>
+          <t>$87.28</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$90.54</t>
+          <t>$87.28</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1237,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $90.54 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $87.28 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$101.59</t>
+          <t>$94.65</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$101.59</t>
+          <t>$94.65</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1284,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $101.59 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $94.65 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,421.10</t>
+          <t>$4,558.70</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,421.10</t>
+          <t>$4,558.70</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1321,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,421 ▬ (-11.6% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,559 ▬ (-6.8% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.395</t>
+          <t>$5.538</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1368,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.395 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.538 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1407,12 +1404,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>90bps</t>
+          <t>88bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-2.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1420,7 +1417,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1444,32 +1441,32 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>319bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>324bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>327bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-3.000</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
+          <t>-5.000</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 324bps ▬. Moderate risk premium.</t>
+          <t>HY spread at 319bps ▬. Moderate risk premium.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1501,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 26.25 ▬. Elevated anxiety; above 20 = fear zone.</t>
+          <t>VIX at 26.00 ▬. Elevated anxiety; above 20 = fear zone.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>99.32</t>
+          <t>99.30</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>99.32</t>
+          <t>99.30</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1538,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 99.32 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 99.30 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,581</t>
+          <t>6,556</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,581</t>
+          <t>6,556</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1634,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,581 ▬. Below 200-day SMA (6,625) — trend broken. -5.7% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,556 ▬. Below 200-day SMA (6,628) — trend broken. -6.1% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>46,208</t>
+          <t>46,124</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>46,208</t>
+          <t>46,124</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1671,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 46,208 ▬.</t>
+          <t>Dow Jones at 46,124 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>21,947</t>
+          <t>21,762</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>21,947</t>
+          <t>21,762</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1718,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 21,947 ▬. Below 200-day SMA — tech trend under pressure.</t>
+          <t>Nasdaq at 21,762 ▬. Below 200-day SMA — tech trend under pressure.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>10,045</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>10,045</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1755,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 9,904 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,045 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1784,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>52,252</t>
+          <t>53,750</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>52,252</t>
+          <t>53,750</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1812,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 52,252 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 53,750 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2017,88 +2014,88 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-24 10:13 UTC</t>
-        </is>
-      </c>
-      <c r="B2" s="25" t="n">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>2026-03-25 10:13 UTC</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n">
         <v>3.75</v>
       </c>
-      <c r="C2" s="25" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="D2" s="25" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E2" s="25" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="F2" s="25" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G2" s="25" t="n">
+      <c r="C2" s="24" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="D2" s="24" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="E2" s="24" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="F2" s="24" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G2" s="24" t="n">
         <v>2.6646</v>
       </c>
-      <c r="H2" s="25" t="n">
+      <c r="H2" s="24" t="n">
         <v>2.7335</v>
       </c>
-      <c r="I2" s="25" t="n">
+      <c r="I2" s="24" t="n">
         <v>3.0557</v>
       </c>
-      <c r="J2" s="25" t="n">
+      <c r="J2" s="24" t="n">
         <v>4.4</v>
       </c>
-      <c r="K2" s="25" t="n">
+      <c r="K2" s="24" t="n">
         <v>205000</v>
       </c>
-      <c r="L2" s="25" t="n">
+      <c r="L2" s="24" t="n">
         <v>-92</v>
       </c>
-      <c r="M2" s="25" t="n"/>
-      <c r="N2" s="25" t="n">
+      <c r="M2" s="24" t="n"/>
+      <c r="N2" s="24" t="n">
         <v>56.4</v>
       </c>
-      <c r="O2" s="25" t="n">
+      <c r="O2" s="24" t="n">
         <v>88</v>
       </c>
-      <c r="P2" s="25" t="n">
-        <v>324</v>
-      </c>
-      <c r="Q2" s="25" t="n">
-        <v>6581</v>
-      </c>
-      <c r="R2" s="25" t="n">
-        <v>46208.4688</v>
-      </c>
-      <c r="S2" s="25" t="n">
-        <v>21946.7598</v>
-      </c>
-      <c r="T2" s="25" t="n">
-        <v>9904.169900000001</v>
-      </c>
-      <c r="U2" s="25" t="n">
-        <v>52252.2812</v>
-      </c>
-      <c r="V2" s="25" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="W2" s="25" t="n">
-        <v>90.54000000000001</v>
-      </c>
-      <c r="X2" s="25" t="n">
-        <v>101.59</v>
-      </c>
-      <c r="Y2" s="25" t="n">
-        <v>4421.1001</v>
-      </c>
-      <c r="Z2" s="25" t="n">
-        <v>5.395</v>
-      </c>
-      <c r="AA2" s="25" t="n">
-        <v>99.321</v>
-      </c>
-      <c r="AB2" s="25" t="n"/>
+      <c r="P2" s="24" t="n">
+        <v>319</v>
+      </c>
+      <c r="Q2" s="24" t="n">
+        <v>6556.3701</v>
+      </c>
+      <c r="R2" s="24" t="n">
+        <v>46124.0586</v>
+      </c>
+      <c r="S2" s="24" t="n">
+        <v>21761.8945</v>
+      </c>
+      <c r="T2" s="24" t="n">
+        <v>10045.21</v>
+      </c>
+      <c r="U2" s="24" t="n">
+        <v>53749.6211</v>
+      </c>
+      <c r="V2" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="W2" s="24" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="X2" s="24" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="Y2" s="24" t="n">
+        <v>4558.7002</v>
+      </c>
+      <c r="Z2" s="24" t="n">
+        <v>5.5385</v>
+      </c>
+      <c r="AA2" s="24" t="n">
+        <v>99.298</v>
+      </c>
+      <c r="AB2" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2167,7 +2164,7 @@
           <t>FED_FUNDS</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Fed Funds Rate</t>
         </is>
@@ -2204,7 +2201,7 @@
           <t>US_2Y</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>US 2Y Treasury</t>
         </is>
@@ -2241,7 +2238,7 @@
           <t>US_10Y</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>US 10Y Treasury</t>
         </is>
@@ -2278,7 +2275,7 @@
           <t>US_30Y</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>US 30Y Treasury</t>
         </is>
@@ -2315,7 +2312,7 @@
           <t>SPREAD_2S10S</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>2s10s Yield Spread</t>
         </is>
@@ -2352,7 +2349,7 @@
           <t>CPI_YOY</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>CPI YoY</t>
         </is>
@@ -2389,7 +2386,7 @@
           <t>CORE_CPI_YOY</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Core CPI YoY</t>
         </is>
@@ -2426,7 +2423,7 @@
           <t>CORE_PCE_YOY</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Core PCE YoY</t>
         </is>
@@ -2463,7 +2460,7 @@
           <t>UNEMPLOYMENT</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Unemployment Rate</t>
         </is>
@@ -2500,7 +2497,7 @@
           <t>INITIAL_CLAIMS</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Initial Jobless Claims</t>
         </is>
@@ -2537,7 +2534,7 @@
           <t>NFP</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Nonfarm Payrolls MoM</t>
         </is>
@@ -2574,7 +2571,7 @@
           <t>ISM_MFG</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>ISM Manufacturing PMI</t>
         </is>
@@ -2611,7 +2608,7 @@
           <t>CONSUMER_CONF</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Consumer Confidence (Mich)</t>
         </is>
@@ -2648,7 +2645,7 @@
           <t>IG_SPREAD</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>IG Credit Spread</t>
         </is>
@@ -2685,7 +2682,7 @@
           <t>HY_SPREAD</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>HY Credit Spread</t>
         </is>
@@ -2722,7 +2719,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
@@ -2759,7 +2756,7 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
@@ -2796,7 +2793,7 @@
           <t>DOW</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Dow Jones</t>
         </is>
@@ -2833,7 +2830,7 @@
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Nasdaq Composite</t>
         </is>
@@ -2870,7 +2867,7 @@
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>FTSE 100</t>
         </is>
@@ -2907,7 +2904,7 @@
           <t>NIKKEI</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Nikkei 225</t>
         </is>
@@ -2944,7 +2941,7 @@
           <t>OIL_WTI</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>WTI Crude Oil</t>
         </is>
@@ -2981,7 +2978,7 @@
           <t>OIL_BRT</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Brent Crude Oil</t>
         </is>
@@ -3018,7 +3015,7 @@
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
@@ -3055,7 +3052,7 @@
           <t>COPPER</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Copper</t>
         </is>
@@ -3092,7 +3089,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>DXY Dollar Index</t>
         </is>
@@ -3129,7 +3126,7 @@
           <t>PUT_CALL</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Put/Call Ratio</t>
         </is>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,10 +72,9 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="9"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -89,9 +88,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -181,34 +181,37 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-25 10:13 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-03-26 10:29 UTC</t>
         </is>
       </c>
     </row>
@@ -706,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.90%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.83%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.88%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>+0.070</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.83% ▬ (-5bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.90% ▲ (+7bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -748,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.39%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.34%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.39%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>+0.050</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -768,12 +771,12 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.34% ▬ (-5bps). Yield within recent range.</t>
+          <t>10Y yield at 4.39% ▬ (+5bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -790,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.94%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.91%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.96%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>+0.030</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.91% ▬ (-5bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.94% ▬ (+3bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -837,17 +840,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -857,7 +860,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.49% ▼. Flat curve; economic uncertainty persists.</t>
+          <t>2s10s spread at 0.49% ▬. Flat curve; economic uncertainty persists.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -894,12 +897,12 @@
           <t>+0.100</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -936,12 +939,12 @@
           <t>-8000.000</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -978,12 +981,12 @@
           <t>-218.000</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1020,7 +1023,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1062,12 +1065,12 @@
           <t>+3.500</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1111,7 +1114,7 @@
           <t>-0.164</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1153,7 +1156,7 @@
           <t>-0.216</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1200,7 +1203,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1224,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$87.28</t>
+          <t>$93.23</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$87.28</t>
+          <t>$93.23</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1237,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $87.28 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $93.23 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$94.65</t>
+          <t>$100.28</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$94.65</t>
+          <t>$100.28</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1284,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $94.65 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $100.28 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,558.70</t>
+          <t>$4,432.40</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,558.70</t>
+          <t>$4,432.40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1321,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,559 ▬ (-6.8% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,432 ▬ (-3.7% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.538</t>
+          <t>$5.513</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1368,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.538 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.513 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1399,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>87bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>88bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>88bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>-1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1417,14 +1420,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 88bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 87bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1446,15 +1449,15 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>324bps</t>
+          <t>319bps</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-5.000</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1483,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1501,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 26.00 ▬. Elevated anxiety; above 20 = fear zone.</t>
+          <t>VIX at 27.15 ▬. Elevated anxiety; above 20 = fear zone.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>99.30</t>
+          <t>99.65</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>99.30</t>
+          <t>99.65</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1538,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 99.30 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 99.65 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,556</t>
+          <t>6,592</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,556</t>
+          <t>6,592</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1634,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,556 ▬. Below 200-day SMA (6,628) — trend broken. -6.1% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,592 ▬. Below 200-day SMA (6,631) — trend broken. -5.5% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>46,124</t>
+          <t>46,429</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>46,124</t>
+          <t>46,429</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1671,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 46,124 ▬.</t>
+          <t>Dow Jones at 46,429 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>21,762</t>
+          <t>21,930</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>21,762</t>
+          <t>21,930</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1718,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 21,762 ▬. Below 200-day SMA — tech trend under pressure.</t>
+          <t>Nasdaq at 21,930 ▬. Below 200-day SMA — tech trend under pressure.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,045</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,045</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1755,7 +1758,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1767,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,045 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,000 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1784,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>53,750</t>
+          <t>53,604</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>53,750</t>
+          <t>53,604</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1809,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 53,750 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 53,604 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2014,88 +2017,88 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-25 10:13 UTC</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>2026-03-26 10:29 UTC</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
-      <c r="C2" s="24" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="D2" s="24" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="E2" s="24" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="F2" s="24" t="n">
+      <c r="C2" s="25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D2" s="25" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E2" s="25" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="F2" s="25" t="n">
         <v>0.49</v>
       </c>
-      <c r="G2" s="24" t="n">
+      <c r="G2" s="25" t="n">
         <v>2.6646</v>
       </c>
-      <c r="H2" s="24" t="n">
+      <c r="H2" s="25" t="n">
         <v>2.7335</v>
       </c>
-      <c r="I2" s="24" t="n">
+      <c r="I2" s="25" t="n">
         <v>3.0557</v>
       </c>
-      <c r="J2" s="24" t="n">
+      <c r="J2" s="25" t="n">
         <v>4.4</v>
       </c>
-      <c r="K2" s="24" t="n">
+      <c r="K2" s="25" t="n">
         <v>205000</v>
       </c>
-      <c r="L2" s="24" t="n">
+      <c r="L2" s="25" t="n">
         <v>-92</v>
       </c>
-      <c r="M2" s="24" t="n"/>
-      <c r="N2" s="24" t="n">
+      <c r="M2" s="25" t="n"/>
+      <c r="N2" s="25" t="n">
         <v>56.4</v>
       </c>
-      <c r="O2" s="24" t="n">
-        <v>88</v>
-      </c>
-      <c r="P2" s="24" t="n">
+      <c r="O2" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="P2" s="25" t="n">
         <v>319</v>
       </c>
-      <c r="Q2" s="24" t="n">
-        <v>6556.3701</v>
-      </c>
-      <c r="R2" s="24" t="n">
-        <v>46124.0586</v>
-      </c>
-      <c r="S2" s="24" t="n">
-        <v>21761.8945</v>
-      </c>
-      <c r="T2" s="24" t="n">
-        <v>10045.21</v>
-      </c>
-      <c r="U2" s="24" t="n">
-        <v>53749.6211</v>
-      </c>
-      <c r="V2" s="24" t="n">
-        <v>26</v>
-      </c>
-      <c r="W2" s="24" t="n">
-        <v>87.28</v>
-      </c>
-      <c r="X2" s="24" t="n">
-        <v>94.65000000000001</v>
-      </c>
-      <c r="Y2" s="24" t="n">
-        <v>4558.7002</v>
-      </c>
-      <c r="Z2" s="24" t="n">
-        <v>5.5385</v>
-      </c>
-      <c r="AA2" s="24" t="n">
-        <v>99.298</v>
-      </c>
-      <c r="AB2" s="24" t="n"/>
+      <c r="Q2" s="25" t="n">
+        <v>6591.8999</v>
+      </c>
+      <c r="R2" s="25" t="n">
+        <v>46429.4883</v>
+      </c>
+      <c r="S2" s="25" t="n">
+        <v>21929.8262</v>
+      </c>
+      <c r="T2" s="25" t="n">
+        <v>10000.4902</v>
+      </c>
+      <c r="U2" s="25" t="n">
+        <v>53603.6484</v>
+      </c>
+      <c r="V2" s="25" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="W2" s="25" t="n">
+        <v>93.23</v>
+      </c>
+      <c r="X2" s="25" t="n">
+        <v>100.28</v>
+      </c>
+      <c r="Y2" s="25" t="n">
+        <v>4432.3999</v>
+      </c>
+      <c r="Z2" s="25" t="n">
+        <v>5.513</v>
+      </c>
+      <c r="AA2" s="25" t="n">
+        <v>99.649</v>
+      </c>
+      <c r="AB2" s="25" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2164,7 +2167,7 @@
           <t>FED_FUNDS</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Fed Funds Rate</t>
         </is>
@@ -2201,7 +2204,7 @@
           <t>US_2Y</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>US 2Y Treasury</t>
         </is>
@@ -2238,7 +2241,7 @@
           <t>US_10Y</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>US 10Y Treasury</t>
         </is>
@@ -2275,7 +2278,7 @@
           <t>US_30Y</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>US 30Y Treasury</t>
         </is>
@@ -2312,7 +2315,7 @@
           <t>SPREAD_2S10S</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>2s10s Yield Spread</t>
         </is>
@@ -2349,7 +2352,7 @@
           <t>CPI_YOY</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>CPI YoY</t>
         </is>
@@ -2386,7 +2389,7 @@
           <t>CORE_CPI_YOY</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Core CPI YoY</t>
         </is>
@@ -2423,7 +2426,7 @@
           <t>CORE_PCE_YOY</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Core PCE YoY</t>
         </is>
@@ -2460,7 +2463,7 @@
           <t>UNEMPLOYMENT</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Unemployment Rate</t>
         </is>
@@ -2497,7 +2500,7 @@
           <t>INITIAL_CLAIMS</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Initial Jobless Claims</t>
         </is>
@@ -2534,7 +2537,7 @@
           <t>NFP</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Nonfarm Payrolls MoM</t>
         </is>
@@ -2571,7 +2574,7 @@
           <t>ISM_MFG</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>ISM Manufacturing PMI</t>
         </is>
@@ -2608,7 +2611,7 @@
           <t>CONSUMER_CONF</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Consumer Confidence (Mich)</t>
         </is>
@@ -2645,7 +2648,7 @@
           <t>IG_SPREAD</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>IG Credit Spread</t>
         </is>
@@ -2682,7 +2685,7 @@
           <t>HY_SPREAD</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>HY Credit Spread</t>
         </is>
@@ -2719,7 +2722,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
@@ -2756,7 +2759,7 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
@@ -2793,7 +2796,7 @@
           <t>DOW</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Dow Jones</t>
         </is>
@@ -2830,7 +2833,7 @@
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Nasdaq Composite</t>
         </is>
@@ -2867,7 +2870,7 @@
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>FTSE 100</t>
         </is>
@@ -2904,7 +2907,7 @@
           <t>NIKKEI</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Nikkei 225</t>
         </is>
@@ -2941,7 +2944,7 @@
           <t>OIL_WTI</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>WTI Crude Oil</t>
         </is>
@@ -2978,7 +2981,7 @@
           <t>OIL_BRT</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Brent Crude Oil</t>
         </is>
@@ -3015,7 +3018,7 @@
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
@@ -3052,7 +3055,7 @@
           <t>COPPER</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Copper</t>
         </is>
@@ -3089,7 +3092,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>DXY Dollar Index</t>
         </is>
@@ -3126,7 +3129,7 @@
           <t>PUT_CALL</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Put/Call Ratio</t>
         </is>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -73,8 +73,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -84,14 +90,8 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -190,28 +190,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-26 10:29 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-03-27 10:11 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.84%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.90%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.83%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.070</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>▼</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.90% ▲ (+7bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.84% ▼ (-6bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,32 +751,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.33%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.39%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.34%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.050</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>-0.060</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.39% ▬ (+5bps). Yield within recent range.</t>
+          <t>10Y yield at 4.33% ▼ (-6bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.94%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.91%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.030</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.94% ▬ (+3bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.89% ▼ (-5bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,22 +835,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.49%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.49% ▬. Flat curve; economic uncertainty persists.</t>
+          <t>2s10s spread at 0.46% ▼. Flat curve; economic uncertainty persists.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,12 +897,12 @@
           <t>+0.100</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -926,32 +926,32 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
           <t>205K</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>-8000.000</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
+          <t>+5000.000</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Initial claims at 205K ▼. Sub-220K — historically tight labor market.</t>
+          <t>Initial claims at 210K ▲. Sub-220K — historically tight labor market.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -981,12 +981,12 @@
           <t>-218.000</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1065,12 +1065,12 @@
           <t>+3.500</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>-0.164</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1156,12 +1156,12 @@
           <t>-0.216</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1203,7 +1203,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$93.23</t>
+          <t>$96.12</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$93.23</t>
+          <t>$96.12</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $93.23 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $96.12 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$100.28</t>
+          <t>$103.29</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$100.28</t>
+          <t>$103.29</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $100.28 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $103.29 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,432.40</t>
+          <t>$4,457.30</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,432.40</t>
+          <t>$4,457.30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,432 ▬ (-3.7% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,457 ▬ (-2.5% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.513</t>
+          <t>$5.483</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.513 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.483 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>88bps</t>
+          <t>87bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1444,32 +1444,32 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>317bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>319bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>319bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
+          <t>-2.000</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 319bps ▬. Moderate risk premium.</t>
+          <t>HY spread at 317bps ▬. Moderate risk premium.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 27.15 ▬. Elevated anxiety; above 20 = fear zone.</t>
+          <t>VIX at 28.72 ▬. Elevated anxiety; above 20 = fear zone.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>99.65</t>
+          <t>100.01</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>99.65</t>
+          <t>100.01</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 99.65 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 100.01 ▬. Dollar neutral; tracking rate differential.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,592</t>
+          <t>6,477</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,592</t>
+          <t>6,477</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,592 ▬. Below 200-day SMA (6,631) — trend broken. -5.5% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,477 ▬. Below 200-day SMA (6,633) — trend broken. -7.2% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>46,429</t>
+          <t>45,960</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>46,429</t>
+          <t>45,960</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 46,429 ▬.</t>
+          <t>Dow Jones at 45,960 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>21,930</t>
+          <t>21,408</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>21,930</t>
+          <t>21,408</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 21,930 ▬. Below 200-day SMA — tech trend under pressure.</t>
+          <t>Nasdaq at 21,408 ▬. Below 200-day SMA — tech trend under pressure.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>9,918</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>9,918</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,000 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 9,918 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>53,604</t>
+          <t>53,373</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>53,604</t>
+          <t>53,373</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 53,604 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 53,373 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,23 +2019,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-03-26 10:29 UTC</t>
+          <t>2026-03-27 10:11 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>2.6646</v>
@@ -2050,7 +2050,7 @@
         <v>4.4</v>
       </c>
       <c r="K2" s="25" t="n">
-        <v>205000</v>
+        <v>210000</v>
       </c>
       <c r="L2" s="25" t="n">
         <v>-92</v>
@@ -2063,40 +2063,40 @@
         <v>87</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6591.8999</v>
+        <v>6477.1602</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>46429.4883</v>
+        <v>45960.1094</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>21929.8262</v>
+        <v>21408.0801</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10000.4902</v>
+        <v>9917.8799</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>53603.6484</v>
+        <v>53373.0703</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>27.15</v>
+        <v>28.72</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>93.23</v>
+        <v>96.12</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>100.28</v>
+        <v>103.29</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4432.3999</v>
+        <v>4457.2998</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.513</v>
+        <v>5.4825</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>99.649</v>
+        <v>100.007</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -73,8 +73,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -83,14 +89,8 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -196,22 +196,22 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-27 10:11 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-03-28 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.96%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.84%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.90%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.120</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▼</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.84% ▼ (-6bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.96% ▲ (+12bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,32 +751,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.42%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.33%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.39%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>+0.090</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>▼</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.33% ▼ (-6bps). Yield within recent range.</t>
+          <t>10Y yield at 4.42% ▲ (+9bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.93%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.89%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.94%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
+          <t>+0.040</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.89% ▼ (-5bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.93% ▬ (+4bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.100</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.46% ▼. Flat curve; economic uncertainty persists.</t>
+          <t>2s10s spread at 0.56% ▲. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,12 +897,12 @@
           <t>+0.100</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+5000.000</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>-218.000</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1052,32 +1052,32 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>56.60</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>56.40</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>52.90</t>
-        </is>
-      </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>+3.500</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
+          <t>+0.200</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Consumer confidence at 56.4 ▲. Below 80 — significant pessimism; spending headwinds.</t>
+          <t>Consumer confidence at 56.6 ▬. Below 80 — significant pessimism; spending headwinds.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1114,7 +1114,7 @@
           <t>-0.164</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1156,12 +1156,12 @@
           <t>-0.216</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1203,7 +1203,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$96.12</t>
+          <t>$99.64</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$96.12</t>
+          <t>$99.64</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $96.12 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $99.64 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$103.29</t>
+          <t>$112.57</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$103.29</t>
+          <t>$112.57</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $103.29 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $112.57 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,457.30</t>
+          <t>$4,492.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,457.30</t>
+          <t>$4,492.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,457 ▬ (-2.5% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,492 ▬ (-1.7% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.483</t>
+          <t>$5.467</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.483 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.467 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>88bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>87bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>87bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1420,14 +1420,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 87bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 88bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,32 +1444,32 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>321bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>317bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>319bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-2.000</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
+          <t>+4.000</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 317bps ▬. Moderate risk premium.</t>
+          <t>HY spread at 321bps ▬. Moderate risk premium.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 28.72 ▬. Elevated anxiety; above 20 = fear zone.</t>
+          <t>VIX at 31.05 ▬. Deep fear zone; risk-off sentiment dominant.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>100.15</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>100.01</t>
+          <t>100.15</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 100.01 ▬. Dollar neutral; tracking rate differential.</t>
+          <t>DXY at 100.15 ▬. Dollar neutral; tracking rate differential.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,477</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,477</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,477 ▬. Below 200-day SMA (6,633) — trend broken. -7.2% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,369 ▬. Below 200-day SMA (6,635) — trend broken. -8.7% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>45,960</t>
+          <t>45,167</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>45,960</t>
+          <t>45,167</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 45,960 ▬.</t>
+          <t>Dow Jones at 45,167 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>21,408</t>
+          <t>20,948</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>21,408</t>
+          <t>20,948</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 21,408 ▬. Below 200-day SMA — tech trend under pressure.</t>
+          <t>Nasdaq at 20,948 ▬. Below 200-day SMA — tech trend under pressure.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>9,918</t>
+          <t>9,967</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>9,918</t>
+          <t>9,967</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 9,918 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 9,967 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -2019,23 +2019,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-03-27 10:11 UTC</t>
+          <t>2026-03-28 10:00 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.89</v>
+        <v>4.93</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>2.6646</v>
@@ -2057,46 +2057,46 @@
       </c>
       <c r="M2" s="25" t="n"/>
       <c r="N2" s="25" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6477.1602</v>
+        <v>6368.8501</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>45960.1094</v>
+        <v>45166.6406</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>21408.0801</v>
+        <v>20948.3594</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>9917.8799</v>
+        <v>9967.4004</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>53373.0703</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>28.72</v>
+        <v>31.05</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>96.12</v>
+        <v>99.64</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>103.29</v>
+        <v>112.57</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4457.2998</v>
+        <v>4492</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.4825</v>
+        <v>5.467</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>100.007</v>
+        <v>100.15</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,9 +72,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -83,14 +84,13 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -181,10 +181,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,25 +193,25 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-03-28 10:00 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-10 05:29 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.79%</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.81%</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.120</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>▬</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.96% ▲ (+12bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.79% ▬ (-2bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -761,22 +761,22 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.090</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.42% ▲ (+9bps). Yield within recent range.</t>
+          <t>10Y yield at 4.29% ▬ (-4bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.93% ▬ (+4bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.89% ▬ (-1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.100</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
+          <t>+0.010</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.56% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -884,32 +884,32 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>4.40%</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>4.30%</t>
-        </is>
-      </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>+0.100</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>-0.100</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Unemployment at 4.4% ▲. Labor market normalizing.</t>
+          <t>Unemployment at 4.3% ▼. Labor market normalizing.</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -926,20 +926,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>203K</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>+5000.000</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+          <t>+16000.000</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -951,7 +951,7 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Initial claims at 210K ▲. Sub-220K — historically tight labor market.</t>
+          <t>Initial claims at 219K ▲. Sub-220K — historically tight labor market.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -968,32 +968,32 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>-92K</t>
+          <t>+178K</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>+126K</t>
+          <t>-133K</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>-218.000</t>
+          <t>+311.000</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>NFP at -92K ▼. Negative prints — labor market contraction signal.</t>
+          <t>NFP at +178K ▲. Solid print; labor market resilient.</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1070,7 +1070,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>-0.164</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1185,32 +1185,32 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>+0.050</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
+          <t>-0.083</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Core PCE at 3.1% YoY ▬. Fed's preferred gauge above target — limits easing.</t>
+          <t>Core PCE at 3.0% YoY ▼. Fed's preferred gauge above target — limits easing.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$99.64</t>
+          <t>$98.37</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$99.64</t>
+          <t>$98.37</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $99.64 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $98.37 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$112.57</t>
+          <t>$96.71</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$112.57</t>
+          <t>$96.71</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $112.57 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $96.71 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,492.00</t>
+          <t>$4,783.80</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,492.00</t>
+          <t>$4,783.80</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,492 ▬ (-1.7% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,784 ▬ (+2.8% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.467</t>
+          <t>$5.781</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.467 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.781 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>88bps</t>
+          <t>83bps</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>87bps</t>
+          <t>86bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>-3.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1420,14 +1420,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 88bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 83bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,32 +1444,32 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>321bps</t>
+          <t>294bps</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>317bps</t>
+          <t>312bps</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+4.000</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>-18.000</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 321bps ▬. Moderate risk premium.</t>
+          <t>HY spread at 294bps ▼. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 31.05 ▬. Deep fear zone; risk-off sentiment dominant.</t>
+          <t>VIX at 19.49 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>100.15</t>
+          <t>98.90</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>100.15</t>
+          <t>98.90</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 100.15 ▬. Dollar neutral; tracking rate differential.</t>
+          <t>DXY at 98.90 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,825</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,825</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,369 ▬. Below 200-day SMA (6,635) — trend broken. -8.7% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,825 ▬. Above 50-day SMA (6,765) — uptrend intact. -2.2% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>45,167</t>
+          <t>48,186</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>45,167</t>
+          <t>48,186</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 45,167 ▬.</t>
+          <t>Dow Jones at 48,186 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>20,948</t>
+          <t>22,822</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>20,948</t>
+          <t>22,822</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 20,948 ▬. Below 200-day SMA — tech trend under pressure.</t>
+          <t>Nasdaq at 22,822 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>9,967</t>
+          <t>10,604</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>9,967</t>
+          <t>10,604</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 9,967 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,604 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>53,373</t>
+          <t>56,999</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>53,373</t>
+          <t>56,999</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1805,14 +1805,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 53,373 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 56,999 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,23 +2019,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-03-28 10:00 UTC</t>
+          <t>2026-04-10 05:29 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.96</v>
+        <v>3.79</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.42</v>
+        <v>4.29</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.93</v>
+        <v>4.89</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>2.6646</v>
@@ -2044,59 +2044,59 @@
         <v>2.7335</v>
       </c>
       <c r="I2" s="25" t="n">
-        <v>3.0557</v>
+        <v>2.9678</v>
       </c>
       <c r="J2" s="25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2" s="25" t="n">
-        <v>210000</v>
+        <v>219000</v>
       </c>
       <c r="L2" s="25" t="n">
-        <v>-92</v>
+        <v>178</v>
       </c>
       <c r="M2" s="25" t="n"/>
       <c r="N2" s="25" t="n">
         <v>56.6</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6368.8501</v>
+        <v>6824.6602</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>45166.6406</v>
+        <v>48185.8008</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>20948.3594</v>
+        <v>22822.4199</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>9967.4004</v>
+        <v>10603.5</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>53373.0703</v>
+        <v>56999.1719</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>31.05</v>
+        <v>19.49</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>99.64</v>
+        <v>98.37</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>112.57</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4492</v>
+        <v>4783.7998</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.467</v>
+        <v>5.7815</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>100.15</v>
+        <v>98.90300000000001</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-10 05:29 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-10 10:32 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$98.37</t>
+          <t>$98.58</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$98.37</t>
+          <t>$98.58</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $98.37 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $98.58 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$96.71</t>
+          <t>$96.55</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$96.71</t>
+          <t>$96.55</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $96.71 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $96.55 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,783.80</t>
+          <t>$4,776.40</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,783.80</t>
+          <t>$4,776.40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,784 ▬ (+2.8% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,776 ▬ (+2.7% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.781</t>
+          <t>$5.810</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.781 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.810 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.49 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.48 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.90</t>
+          <t>98.79</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.90</t>
+          <t>98.79</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.90 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.79 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,604</t>
+          <t>10,632</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,604</t>
+          <t>10,632</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,604 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,632 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>56,999</t>
+          <t>56,924</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>56,999</t>
+          <t>56,924</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 56,999 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 56,924 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-10 05:29 UTC</t>
+          <t>2026-04-10 10:32 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2075,28 +2075,28 @@
         <v>22822.4199</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10603.5</v>
+        <v>10632.04</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>56999.1719</v>
+        <v>56924.1094</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>19.49</v>
+        <v>19.48</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>98.37</v>
+        <v>98.58</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>96.70999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4783.7998</v>
+        <v>4776.3999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.7815</v>
+        <v>5.8095</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.90300000000001</v>
+        <v>98.791</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-10 10:32 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-10 14:33 UTC</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
+          <t>3.32%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
           <t>2.66%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2.83%</t>
-        </is>
-      </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>-0.164</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.656</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>CPI at 2.7% YoY ▼. Approaching target but sticky; last-mile inflation challenge.</t>
+          <t>CPI at 3.3% YoY ▲. Above Fed target; disinflation progress stalling.</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1143,17 +1143,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
+          <t>2.67%</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
           <t>2.73%</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>2.95%</t>
-        </is>
-      </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>-0.216</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$98.58</t>
+          <t>$97.69</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$98.58</t>
+          <t>$97.69</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $98.58 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $97.69 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$96.55</t>
+          <t>$95.56</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$96.55</t>
+          <t>$95.56</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $96.55 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $95.56 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,776.40</t>
+          <t>$4,812.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,776.40</t>
+          <t>$4,812.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,776 ▬ (+2.7% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,813 ▬ (+3.5% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.810</t>
+          <t>$5.930</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.810 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.930 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>86bps</t>
+          <t>83bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-3.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>290bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>294bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>312bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-18.000</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>-4.000</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 294bps ▼. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 290bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.48 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.93 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.79</t>
+          <t>98.55</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.79</t>
+          <t>98.55</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.79 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.55 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,825</t>
+          <t>6,841</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,825</t>
+          <t>6,841</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,825 ▬. Above 50-day SMA (6,765) — uptrend intact. -2.2% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,841 ▬. Above 50-day SMA (6,762) — uptrend intact. -2.0% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,186</t>
+          <t>48,095</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,186</t>
+          <t>48,095</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,186 ▬.</t>
+          <t>Dow Jones at 48,095 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>22,822</t>
+          <t>22,985</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>22,822</t>
+          <t>22,985</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 22,822 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 22,985 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,632</t>
+          <t>10,625</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,632</t>
+          <t>10,625</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,632 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,625 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-10 10:32 UTC</t>
+          <t>2026-04-10 14:33 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2038,10 +2038,10 @@
         <v>0.51</v>
       </c>
       <c r="G2" s="25" t="n">
-        <v>2.6646</v>
+        <v>3.3202</v>
       </c>
       <c r="H2" s="25" t="n">
-        <v>2.7335</v>
+        <v>2.6731</v>
       </c>
       <c r="I2" s="25" t="n">
         <v>2.9678</v>
@@ -2063,40 +2063,40 @@
         <v>83</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6824.6602</v>
+        <v>6841.3701</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48185.8008</v>
+        <v>48095.25</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>22822.4199</v>
+        <v>22984.9648</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10632.04</v>
+        <v>10625.2803</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>56924.1094</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>19.48</v>
+        <v>18.93</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>98.58</v>
+        <v>97.69</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>96.55</v>
+        <v>95.56</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4776.3999</v>
+        <v>4812.6001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.8095</v>
+        <v>5.93</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.791</v>
+        <v>98.55200000000001</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-10 14:33 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-10 21:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$97.69</t>
+          <t>$95.63</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$97.69</t>
+          <t>$95.63</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $97.69 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $95.63 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$95.56</t>
+          <t>$94.45</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$95.56</t>
+          <t>$94.45</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $95.56 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $94.45 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,812.60</t>
+          <t>$4,771.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,812.60</t>
+          <t>$4,771.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,813 ▬ (+3.5% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
+          <t>Gold at $4,771 ▬ (+2.6% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.930</t>
+          <t>$5.868</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.930 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.868 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.93 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.23 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.55</t>
+          <t>98.70</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.55</t>
+          <t>98.70</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.55 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.70 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,841</t>
+          <t>6,817</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,841</t>
+          <t>6,817</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,841 ▬. Above 50-day SMA (6,762) — uptrend intact. -2.0% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,817 ▬. Above 50-day SMA (6,762) — uptrend intact. -2.3% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,095</t>
+          <t>47,917</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,095</t>
+          <t>47,917</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,095 ▬.</t>
+          <t>Dow Jones at 47,917 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>22,985</t>
+          <t>22,903</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>22,985</t>
+          <t>22,903</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 22,985 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 22,903 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,625</t>
+          <t>10,601</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,625</t>
+          <t>10,601</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,625 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,601 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>56,924</t>
+          <t>55,895</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
+          <t>+1028.790</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>▲</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 56,924 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 56,924 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-10 14:33 UTC</t>
+          <t>2026-04-10 21:46 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2066,37 +2066,37 @@
         <v>290</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6841.3701</v>
+        <v>6816.8901</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48095.25</v>
+        <v>47916.5703</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>22984.9648</v>
+        <v>22902.8945</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10625.2803</v>
+        <v>10600.5303</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>56924.1094</v>
+        <v>56924.11</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.93</v>
+        <v>19.23</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>97.69</v>
+        <v>95.63</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>95.56</v>
+        <v>94.45</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4812.6001</v>
+        <v>4771</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.93</v>
+        <v>5.868</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.55200000000001</v>
+        <v>98.69799999999999</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -74,12 +74,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="00FF4D4D"/>
       <sz val="9"/>
     </font>
@@ -92,6 +86,12 @@
       <b val="1"/>
       <color rgb="00FF4D4D"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -190,28 +190,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-10 21:46 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-11 10:02 UTC</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.79%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.81%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.79% ▬ (-2bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.78% ▬ (-1bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -769,14 +769,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.29% ▬ (-4bps). Yield within recent range.</t>
+          <t>10Y yield at 4.29% ▬ (+0bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.89%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -811,14 +811,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.89% ▬ (-1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.90% ▬ (+1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,17 +835,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.51%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -853,14 +853,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.50% ▬. Flat curve; economic uncertainty persists.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+16000.000</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$95.63</t>
+          <t>$96.57</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$95.63</t>
+          <t>$96.57</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1245,14 +1245,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $95.63 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $96.57 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$94.45</t>
+          <t>$95.20</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$94.45</t>
+          <t>$95.20</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $94.45 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $95.20 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,771.00</t>
+          <t>$4,761.90</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,771.00</t>
+          <t>$4,761.90</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1329,14 +1329,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,771 ▬ (+2.6% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,762 ▬ (+2.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.868</t>
+          <t>$5.871</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.868 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.871 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1462,7 +1462,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.70</t>
+          <t>98.65</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.70</t>
+          <t>98.65</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.70 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.65 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1637,7 +1637,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1721,7 +1721,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,601</t>
+          <t>10,600</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,601</t>
+          <t>10,600</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,601 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,600 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>55,895</t>
+          <t>56,924</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+1028.790</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 56,924 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 56,924 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,23 +2019,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-10 21:46 UTC</t>
+          <t>2026-04-11 10:02 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="D2" s="25" t="n">
         <v>4.29</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2072,31 +2072,31 @@
         <v>47916.5703</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>22902.8945</v>
+        <v>22902.8906</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10600.5303</v>
+        <v>10600.5</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>56924.11</v>
+        <v>56924.1094</v>
       </c>
       <c r="V2" s="25" t="n">
         <v>19.23</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>95.63</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>94.45</v>
+        <v>95.2</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4771</v>
+        <v>4761.8999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.868</v>
+        <v>5.8705</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.69799999999999</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-11 10:02 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-12 10:04 UTC</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,761.90</t>
+          <t>$4,787.40</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,761.90</t>
+          <t>$4,787.40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,762 ▬ (+2.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,787 ▬ (+2.9% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.871</t>
+          <t>$5.886</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.871 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.886 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1528,17 +1528,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
+          <t>98.70</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
           <t>98.65</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>98.65</t>
-        </is>
-      </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+0.048</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.65 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.70 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-11 10:02 UTC</t>
+          <t>2026-04-12 10:04 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2090,13 +2090,13 @@
         <v>95.2</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4761.8999</v>
+        <v>4787.3999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.8705</v>
+        <v>5.886</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.65000000000001</v>
+        <v>98.69799999999999</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-12 10:04 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-13 10:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$96.57</t>
+          <t>$103.90</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$96.57</t>
+          <t>$103.90</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $96.57 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $103.90 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$95.20</t>
+          <t>$102.02</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$95.20</t>
+          <t>$102.02</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $95.20 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $102.02 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,787.40</t>
+          <t>$4,743.20</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,787.40</t>
+          <t>$4,743.20</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,787 ▬ (+2.9% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,743 ▬ (+1.9% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.886</t>
+          <t>$5.853</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.886 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.853 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.23 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 21.31 ▬. Elevated anxiety; above 20 = fear zone.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,17 +1528,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.70</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.65</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>+0.048</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.70 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.94 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,600</t>
+          <t>10,563</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,600</t>
+          <t>10,563</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,600 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,563 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>56,924</t>
+          <t>56,503</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>56,924</t>
+          <t>56,503</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 56,924 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 56,503 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-12 10:04 UTC</t>
+          <t>2026-04-13 10:59 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2075,28 +2075,28 @@
         <v>22902.8906</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10600.5</v>
+        <v>10562.75</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>56924.1094</v>
+        <v>56502.7695</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>19.23</v>
+        <v>21.31</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>96.56999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>95.2</v>
+        <v>102.02</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4787.3999</v>
+        <v>4743.2002</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.886</v>
+        <v>5.8535</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.69799999999999</v>
+        <v>98.938</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-13 10:59 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-13 14:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$103.90</t>
+          <t>$102.49</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$103.90</t>
+          <t>$102.49</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $103.90 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $102.49 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$102.02</t>
+          <t>$100.86</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$102.02</t>
+          <t>$100.86</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $102.02 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $100.86 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,743.20</t>
+          <t>$4,739.40</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,743.20</t>
+          <t>$4,739.40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,743 ▬ (+1.9% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,739 ▬ (+1.8% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.853</t>
+          <t>$5.966</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.853 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.966 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>82bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>83bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>83bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>-1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 83bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 82bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>294bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>290bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>294bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-4.000</t>
+          <t>+4.000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 290bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 294bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1504,14 +1504,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 21.31 ▬. Elevated anxiety; above 20 = fear zone.</t>
+          <t>VIX at 19.88 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>98.70</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>98.70</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.94 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.70 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,817</t>
+          <t>6,830</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,817</t>
+          <t>6,830</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,817 ▬. Above 50-day SMA (6,762) — uptrend intact. -2.3% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,830 ▬. Above 50-day SMA (6,759) — uptrend intact. -2.1% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>47,917</t>
+          <t>47,737</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>47,917</t>
+          <t>47,737</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 47,917 ▬.</t>
+          <t>Dow Jones at 47,737 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>22,903</t>
+          <t>23,007</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>22,903</t>
+          <t>23,007</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 22,903 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 23,007 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,563</t>
+          <t>10,589</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,563</t>
+          <t>10,589</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,563 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,589 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-13 10:59 UTC</t>
+          <t>2026-04-13 14:59 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2060,43 +2060,43 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6816.8901</v>
+        <v>6829.5298</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>47916.5703</v>
+        <v>47736.5781</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>22902.8906</v>
+        <v>23006.5293</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10562.75</v>
+        <v>10589.4199</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>56502.7695</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>21.31</v>
+        <v>19.88</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>103.9</v>
+        <v>102.49</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>102.02</v>
+        <v>100.86</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4743.2002</v>
+        <v>4739.3999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.8535</v>
+        <v>5.9665</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.938</v>
+        <v>98.70399999999999</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -79,11 +79,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
@@ -92,6 +87,11 @@
       <b val="1"/>
       <color rgb="0000E676"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000E676"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -184,22 +184,13 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,10 +199,19 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-13 14:59 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-13 21:55 UTC</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.78%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.78% ▬ (-1bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.81% ▬ (+3bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.31%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.29%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.29%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.29% ▬ (+0bps). Yield within recent range.</t>
+          <t>10Y yield at 4.31% ▬ (+2bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,14 +793,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.90%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.89%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
           <t>+0.010</t>
@@ -811,14 +811,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.90% ▬ (+1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.91% ▬ (+1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.010</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.50% ▬. Flat curve; economic uncertainty persists.</t>
+          <t>2s10s spread at 0.52% ▲. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+16000.000</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1028,7 +1028,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$102.49</t>
+          <t>$98.01</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$102.49</t>
+          <t>$98.01</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1245,14 +1245,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $102.49 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $98.01 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$100.86</t>
+          <t>$98.11</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$100.86</t>
+          <t>$98.11</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $100.86 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $98.11 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,739.40</t>
+          <t>$4,766.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,739.40</t>
+          <t>$4,766.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1329,14 +1329,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,739 ▬ (+1.8% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,767 ▬ (+2.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.966</t>
+          <t>$6.003</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.966 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.003 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1462,7 +1462,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.88 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.12 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.70</t>
+          <t>98.42</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.70</t>
+          <t>98.42</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.70 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.42 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,830</t>
+          <t>6,886</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,830</t>
+          <t>6,886</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,830 ▬. Above 50-day SMA (6,759) — uptrend intact. -2.1% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,886 ▬. Above 50-day SMA (6,760) — uptrend intact. -1.3% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>47,737</t>
+          <t>48,218</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>47,737</t>
+          <t>48,218</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 47,737 ▬.</t>
+          <t>Dow Jones at 48,218 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>23,007</t>
+          <t>23,184</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>23,007</t>
+          <t>23,184</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 23,007 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 23,184 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,589</t>
+          <t>10,583</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,589</t>
+          <t>10,583</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,589 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,583 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>56,503</t>
+          <t>56,924</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
+          <t>-421.339</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 56,503 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 56,503 ▼. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,23 +2019,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-13 14:59 UTC</t>
+          <t>2026-04-13 21:55 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2066,37 +2066,37 @@
         <v>294</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6829.5298</v>
+        <v>6886.2402</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>47736.5781</v>
+        <v>48218.25</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>23006.5293</v>
+        <v>23183.7363</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10589.4199</v>
+        <v>10582.96</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>56502.7695</v>
+        <v>56502.77</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>19.88</v>
+        <v>19.12</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>102.49</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>100.86</v>
+        <v>98.11</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4739.3999</v>
+        <v>4766.6001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.9665</v>
+        <v>6.0035</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.70399999999999</v>
+        <v>98.419</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-13 21:55 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-14 10:43 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$98.01</t>
+          <t>$97.09</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$98.01</t>
+          <t>$97.09</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $98.01 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $97.09 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$98.11</t>
+          <t>$98.91</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$98.11</t>
+          <t>$98.91</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $98.11 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $98.91 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,766.60</t>
+          <t>$4,805.90</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,766.60</t>
+          <t>$4,805.90</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,767 ▬ (+2.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,806 ▬ (+3.2% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.003</t>
+          <t>$6.043</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.003 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.043 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.12 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.34 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.42</t>
+          <t>98.10</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.42</t>
+          <t>98.10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.42 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.10 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,583</t>
+          <t>10,590</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,583</t>
+          <t>10,590</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,583 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,590 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>56,503</t>
+          <t>57,877</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>56,924</t>
+          <t>57,877</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>-421.339</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 56,503 ▼. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 57,877 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-13 21:55 UTC</t>
+          <t>2026-04-14 10:43 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2072,31 +2072,31 @@
         <v>48218.25</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>23183.7363</v>
+        <v>23183.7402</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10582.96</v>
+        <v>10590.0303</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>56502.77</v>
+        <v>57877.3906</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>19.12</v>
+        <v>18.34</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>98.01000000000001</v>
+        <v>97.09</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>98.11</v>
+        <v>98.91</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4766.6001</v>
+        <v>4805.8999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0035</v>
+        <v>6.0435</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.419</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-14 10:43 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-14 14:59 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$97.09</t>
+          <t>$93.31</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$97.09</t>
+          <t>$93.31</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $97.09 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $93.31 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$98.91</t>
+          <t>$95.48</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$98.91</t>
+          <t>$95.48</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $98.91 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $95.48 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,805.90</t>
+          <t>$4,822.20</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,805.90</t>
+          <t>$4,822.20</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,806 ▬ (+3.2% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
+          <t>Gold at $4,822 ▬ (+3.5% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.043</t>
+          <t>$6.085</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.043 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.085 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>83bps</t>
+          <t>82bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>295bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>294bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>290bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+4.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 294bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 295bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.34 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.06 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.10</t>
+          <t>97.99</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.10</t>
+          <t>97.99</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.10 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 97.99 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,886</t>
+          <t>6,941</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,886</t>
+          <t>6,941</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,886 ▬. Above 50-day SMA (6,760) — uptrend intact. -1.3% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,941 ▬. Above 50-day SMA (6,760) — uptrend intact. -0.5% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,218</t>
+          <t>48,496</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,218</t>
+          <t>48,496</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,218 ▬.</t>
+          <t>Dow Jones at 48,496 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>23,184</t>
+          <t>23,481</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>23,184</t>
+          <t>23,481</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 23,184 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 23,481 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-14 10:43 UTC</t>
+          <t>2026-04-14 14:59 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2063,40 +2063,40 @@
         <v>82</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6886.2402</v>
+        <v>6940.5498</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48218.25</v>
+        <v>48496.2891</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>23183.7402</v>
+        <v>23481.1484</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10590.0303</v>
+        <v>10590.4297</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>57877.3906</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.34</v>
+        <v>18.06</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>97.09</v>
+        <v>93.31</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>98.91</v>
+        <v>95.48</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4805.8999</v>
+        <v>4822.2002</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0435</v>
+        <v>6.085</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.09999999999999</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -74,23 +74,23 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FF4D4D"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -190,28 +190,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-14 14:59 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-14 21:56 UTC</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.81%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.78%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.030</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.81% ▬ (+3bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.78% ▬ (-3bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.31%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.29%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.31% ▬ (+2bps). Yield within recent range.</t>
+          <t>10Y yield at 4.30% ▬ (-1bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.91%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -811,14 +811,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.91% ▬ (+1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.90% ▬ (-1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.52%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.52% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.50% ▼. Flat curve; economic uncertainty persists.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+16000.000</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$93.31</t>
+          <t>$92.07</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$93.31</t>
+          <t>$92.07</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1245,14 +1245,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $93.31 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $92.07 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$95.48</t>
+          <t>$95.14</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$95.48</t>
+          <t>$95.14</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $95.48 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $95.14 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,822.20</t>
+          <t>$4,864.50</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,822.20</t>
+          <t>$4,864.50</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1329,14 +1329,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,822 ▬ (+3.5% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
+          <t>Gold at $4,864 ▬ (+4.5% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.085</t>
+          <t>$6.082</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.085 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.082 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1462,7 +1462,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.06 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.36 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>97.99</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>97.99</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 97.99 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.13 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,941</t>
+          <t>6,967</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,941</t>
+          <t>6,967</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,941 ▬. Above 50-day SMA (6,760) — uptrend intact. -0.5% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,967 ▬. Above 50-day SMA (6,761) — uptrend intact. -0.2% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,496</t>
+          <t>48,536</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,496</t>
+          <t>48,536</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,496 ▬.</t>
+          <t>Dow Jones at 48,536 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>23,481</t>
+          <t>23,639</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>23,481</t>
+          <t>23,639</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 23,481 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 23,639 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,590</t>
+          <t>10,609</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,590</t>
+          <t>10,609</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,590 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,609 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>57,877</t>
+          <t>56,503</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
+          <t>+1374.620</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 57,877 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 57,877 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2019,23 +2019,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-14 14:59 UTC</t>
+          <t>2026-04-14 21:56 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2066,37 +2066,37 @@
         <v>295</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6940.5498</v>
+        <v>6967.3799</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48496.2891</v>
+        <v>48535.9883</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>23481.1484</v>
+        <v>23639.084</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10590.4297</v>
+        <v>10609.0596</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>57877.3906</v>
+        <v>57877.39</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.06</v>
+        <v>18.36</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>93.31</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>95.48</v>
+        <v>95.14</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4822.2002</v>
+        <v>4864.5</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.085</v>
+        <v>6.0815</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>97.98999999999999</v>
+        <v>98.129</v>
       </c>
       <c r="AB2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-14 21:56 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-15 16:05 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$92.07</t>
+          <t>$92.27</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$92.07</t>
+          <t>$92.27</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $92.07 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $92.27 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$95.14</t>
+          <t>$95.69</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$95.14</t>
+          <t>$95.69</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $95.14 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $95.69 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,864.50</t>
+          <t>$4,828.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,864.50</t>
+          <t>$4,828.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,864 ▬ (+4.5% wk). Strong weekly gain — inflation hedge / safe haven bid.</t>
+          <t>Gold at $4,828 ▬ (+1.7% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.082</t>
+          <t>$6.076</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.082 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.076 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>81bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>82bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>82bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>-1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 82bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>284bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>295bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>294bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+1.000</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>▬</t>
+          <t>-11.000</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 295bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 284bps ▼. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.36 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.04 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>98.07</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>98.07</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.13 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.07 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,967</t>
+          <t>6,993</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,967</t>
+          <t>6,993</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,967 ▬. Above 50-day SMA (6,761) — uptrend intact. -0.2% from 52-week high.</t>
+          <t>S&amp;P 500 at 6,993 ▬. Above 50-day SMA (6,761) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,536</t>
+          <t>48,293</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,536</t>
+          <t>48,293</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,536 ▬.</t>
+          <t>Dow Jones at 48,293 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>23,639</t>
+          <t>23,880</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>23,639</t>
+          <t>23,880</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 23,639 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 23,880 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,609</t>
+          <t>10,560</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,609</t>
+          <t>10,560</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,609 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,560 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>58,134</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>57,877</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>56,503</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+1374.620</t>
+          <t>+256.849</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 57,877 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 58,134 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1821,12 +1821,104 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🪙  CRYPTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Bitcoin</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>73925.71</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>73925.71</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Bitcoin at 73925.71 ▬. Signal: BEARISH.</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Ethereum</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>2337.49</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>2337.49</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Ethereum at 2337.49 ▬. Signal: BEARISH.</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
   </mergeCells>
@@ -1841,7 +1933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1872,6 +1964,8 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -2012,6 +2106,16 @@
       </c>
       <c r="AB1" s="2" t="inlineStr">
         <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
           <t>PUT_CALL</t>
         </is>
       </c>
@@ -2019,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-14 21:56 UTC</t>
+          <t>2026-04-15 16:05 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2060,45 +2164,51 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6967.3799</v>
+        <v>6993.4399</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48535.9883</v>
+        <v>48293.4688</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>23639.084</v>
+        <v>23880.2441</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10609.0596</v>
+        <v>10559.5801</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>57877.39</v>
+        <v>58134.24</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.36</v>
+        <v>18.04</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>92.06999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>95.14</v>
+        <v>95.69</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4864.5</v>
+        <v>4828</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0815</v>
+        <v>6.0755</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.129</v>
-      </c>
-      <c r="AB2" s="25" t="n"/>
+        <v>98.06699999999999</v>
+      </c>
+      <c r="AB2" s="25" t="n">
+        <v>73925.71090000001</v>
+      </c>
+      <c r="AC2" s="25" t="n">
+        <v>2337.49</v>
+      </c>
+      <c r="AD2" s="25" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -85,12 +85,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -184,11 +184,14 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,22 +199,19 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-15 16:05 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-15 22:08 UTC</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.76%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.78%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.81%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>-0.020</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.78% ▬ (-3bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.76% ▬ (-2bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.30%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.31%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -769,14 +769,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.30% ▬ (-1bps). Yield within recent range.</t>
+          <t>10Y yield at 4.26% ▬ (-4bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.87%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.90%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.91%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -811,14 +811,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.90% ▬ (-1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.87% ▬ (-3bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.030</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.50% ▼. Flat curve; economic uncertainty persists.</t>
+          <t>2s10s spread at 0.53% ▲. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+16000.000</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1028,7 +1028,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$92.27</t>
+          <t>$91.39</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$92.27</t>
+          <t>$91.39</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1245,14 +1245,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $92.27 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $91.39 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$95.69</t>
+          <t>$94.93</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$95.69</t>
+          <t>$94.93</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $95.69 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $94.93 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,828.00</t>
+          <t>$4,813.90</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,828.00</t>
+          <t>$4,813.90</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,828 ▬ (+1.7% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,814 ▬ (+1.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.076</t>
+          <t>$6.078</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.076 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.078 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1462,7 +1462,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>18.17</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>18.17</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.04 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.17 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.07</t>
+          <t>98.08</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.07</t>
+          <t>98.08</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.07 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.08 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>6,993</t>
+          <t>7,023</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>6,993</t>
+          <t>7,023</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 6,993 ▬. Above 50-day SMA (6,761) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,023 ▬. Above 50-day SMA (6,762) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,293</t>
+          <t>48,464</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,293</t>
+          <t>48,464</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,293 ▬.</t>
+          <t>Dow Jones at 48,464 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>23,880</t>
+          <t>24,016</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>23,880</t>
+          <t>24,016</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 23,880 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,016 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1763,7 +1763,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1800,12 +1800,12 @@
           <t>+256.849</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>73925.71</t>
+          <t>75015.72</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>73925.71</t>
+          <t>75015.72</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 73925.71 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 75015.72 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2337.49</t>
+          <t>2373.36</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2337.49</t>
+          <t>2373.36</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1896,14 +1896,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2337.49 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2373.36 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,23 +2123,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-15 16:05 UTC</t>
+          <t>2026-04-15 22:08 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2170,13 +2170,13 @@
         <v>284</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>6993.4399</v>
+        <v>7022.9502</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48293.4688</v>
+        <v>48463.7188</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>23880.2441</v>
+        <v>24016.0176</v>
       </c>
       <c r="T2" s="25" t="n">
         <v>10559.5801</v>
@@ -2185,28 +2185,28 @@
         <v>58134.24</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.04</v>
+        <v>18.17</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>92.27</v>
+        <v>91.39</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>95.69</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4828</v>
+        <v>4813.8999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0755</v>
+        <v>6.0785</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.06699999999999</v>
+        <v>98.08199999999999</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>73925.71090000001</v>
+        <v>75015.7188</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2337.49</v>
+        <v>2373.3601</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -202,16 +202,13 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-15 22:08 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-16 15:03 UTC</t>
         </is>
       </c>
     </row>
@@ -926,22 +923,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>+16000.000</t>
+          <t>-11000.000</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>▼</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -951,7 +948,7 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Initial claims at 219K ▲. Sub-220K — historically tight labor market.</t>
+          <t>Initial claims at 207K ▼. Sub-220K — historically tight labor market.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -1156,7 +1153,7 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1227,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$91.39</t>
+          <t>$90.32</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$91.39</t>
+          <t>$90.32</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1249,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $91.39 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $90.32 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$94.93</t>
+          <t>$97.98</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$94.93</t>
+          <t>$97.98</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1284,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $94.93 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $97.98 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,813.90</t>
+          <t>$4,812.10</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,813.90</t>
+          <t>$4,812.10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1333,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,814 ▬ (+1.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,812 ▬ (+0.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.078</t>
+          <t>$6.069</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1375,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.078 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.069 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,14 +1399,14 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>80bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>81bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>82bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
           <t>-1.000</t>
@@ -1427,7 +1424,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,22 +1441,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>285bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>284bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>295bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-11.000</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>+1.000</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -1469,7 +1466,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 284bps ▼. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 285bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.17 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.84 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.08</t>
+          <t>98.25</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.08</t>
+          <t>98.25</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.08 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.25 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,023</t>
+          <t>7,028</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,023</t>
+          <t>7,028</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1641,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,023 ▬. Above 50-day SMA (6,762) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,028 ▬. Above 50-day SMA (6,764) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,464</t>
+          <t>48,440</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,464</t>
+          <t>48,440</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,464 ▬.</t>
+          <t>Dow Jones at 48,440 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,016</t>
+          <t>24,031</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,016</t>
+          <t>24,031</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1725,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,016 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,031 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,560</t>
+          <t>10,589</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,560</t>
+          <t>10,589</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,560 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,589 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,17 +1784,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>59,518</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>58,134</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>57,877</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+256.849</t>
+          <t>+1384.102</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
@@ -1812,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 58,134 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,518 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>75015.72</t>
+          <t>74019.43</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>75015.72</t>
+          <t>74019.43</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 75015.72 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 74019.43 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2373.36</t>
+          <t>2312.92</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2373.36</t>
+          <t>2312.92</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2373.36 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2312.92 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2121,94 +2118,94 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>2026-04-15 22:08 UTC</t>
-        </is>
-      </c>
-      <c r="B2" s="25" t="n">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-16 15:03 UTC</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n">
         <v>3.75</v>
       </c>
-      <c r="C2" s="25" t="n">
+      <c r="C2" s="24" t="n">
         <v>3.76</v>
       </c>
-      <c r="D2" s="25" t="n">
+      <c r="D2" s="24" t="n">
         <v>4.26</v>
       </c>
-      <c r="E2" s="25" t="n">
+      <c r="E2" s="24" t="n">
         <v>4.87</v>
       </c>
-      <c r="F2" s="25" t="n">
+      <c r="F2" s="24" t="n">
         <v>0.53</v>
       </c>
-      <c r="G2" s="25" t="n">
+      <c r="G2" s="24" t="n">
         <v>3.3202</v>
       </c>
-      <c r="H2" s="25" t="n">
+      <c r="H2" s="24" t="n">
         <v>2.6731</v>
       </c>
-      <c r="I2" s="25" t="n">
+      <c r="I2" s="24" t="n">
         <v>2.9678</v>
       </c>
-      <c r="J2" s="25" t="n">
+      <c r="J2" s="24" t="n">
         <v>4.3</v>
       </c>
-      <c r="K2" s="25" t="n">
-        <v>219000</v>
-      </c>
-      <c r="L2" s="25" t="n">
+      <c r="K2" s="24" t="n">
+        <v>207000</v>
+      </c>
+      <c r="L2" s="24" t="n">
         <v>178</v>
       </c>
-      <c r="M2" s="25" t="n"/>
-      <c r="N2" s="25" t="n">
+      <c r="M2" s="24" t="n"/>
+      <c r="N2" s="24" t="n">
         <v>56.6</v>
       </c>
-      <c r="O2" s="25" t="n">
-        <v>81</v>
-      </c>
-      <c r="P2" s="25" t="n">
-        <v>284</v>
-      </c>
-      <c r="Q2" s="25" t="n">
-        <v>7022.9502</v>
-      </c>
-      <c r="R2" s="25" t="n">
-        <v>48463.7188</v>
-      </c>
-      <c r="S2" s="25" t="n">
-        <v>24016.0176</v>
-      </c>
-      <c r="T2" s="25" t="n">
-        <v>10559.5801</v>
-      </c>
-      <c r="U2" s="25" t="n">
-        <v>58134.24</v>
-      </c>
-      <c r="V2" s="25" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="W2" s="25" t="n">
-        <v>91.39</v>
-      </c>
-      <c r="X2" s="25" t="n">
-        <v>94.93000000000001</v>
-      </c>
-      <c r="Y2" s="25" t="n">
-        <v>4813.8999</v>
-      </c>
-      <c r="Z2" s="25" t="n">
-        <v>6.0785</v>
-      </c>
-      <c r="AA2" s="25" t="n">
-        <v>98.08199999999999</v>
-      </c>
-      <c r="AB2" s="25" t="n">
-        <v>75015.7188</v>
-      </c>
-      <c r="AC2" s="25" t="n">
-        <v>2373.3601</v>
-      </c>
-      <c r="AD2" s="25" t="n"/>
+      <c r="O2" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="P2" s="24" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q2" s="24" t="n">
+        <v>7028.3901</v>
+      </c>
+      <c r="R2" s="24" t="n">
+        <v>48440.2305</v>
+      </c>
+      <c r="S2" s="24" t="n">
+        <v>24030.7832</v>
+      </c>
+      <c r="T2" s="24" t="n">
+        <v>10589.2402</v>
+      </c>
+      <c r="U2" s="24" t="n">
+        <v>59518.34</v>
+      </c>
+      <c r="V2" s="24" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="W2" s="24" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="X2" s="24" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="Y2" s="24" t="n">
+        <v>4812.1001</v>
+      </c>
+      <c r="Z2" s="24" t="n">
+        <v>6.069</v>
+      </c>
+      <c r="AA2" s="24" t="n">
+        <v>98.255</v>
+      </c>
+      <c r="AB2" s="24" t="n">
+        <v>74019.42969999999</v>
+      </c>
+      <c r="AC2" s="24" t="n">
+        <v>2312.9199</v>
+      </c>
+      <c r="AD2" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2277,7 +2274,7 @@
           <t>FED_FUNDS</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Fed Funds Rate</t>
         </is>
@@ -2314,7 +2311,7 @@
           <t>US_2Y</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>US 2Y Treasury</t>
         </is>
@@ -2351,7 +2348,7 @@
           <t>US_10Y</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>US 10Y Treasury</t>
         </is>
@@ -2388,7 +2385,7 @@
           <t>US_30Y</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>US 30Y Treasury</t>
         </is>
@@ -2425,7 +2422,7 @@
           <t>SPREAD_2S10S</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>2s10s Yield Spread</t>
         </is>
@@ -2462,7 +2459,7 @@
           <t>CPI_YOY</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>CPI YoY</t>
         </is>
@@ -2499,7 +2496,7 @@
           <t>CORE_CPI_YOY</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Core CPI YoY</t>
         </is>
@@ -2536,7 +2533,7 @@
           <t>CORE_PCE_YOY</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Core PCE YoY</t>
         </is>
@@ -2573,7 +2570,7 @@
           <t>UNEMPLOYMENT</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Unemployment Rate</t>
         </is>
@@ -2610,7 +2607,7 @@
           <t>INITIAL_CLAIMS</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Initial Jobless Claims</t>
         </is>
@@ -2647,7 +2644,7 @@
           <t>NFP</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Nonfarm Payrolls MoM</t>
         </is>
@@ -2684,7 +2681,7 @@
           <t>ISM_MFG</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>ISM Manufacturing PMI</t>
         </is>
@@ -2721,7 +2718,7 @@
           <t>CONSUMER_CONF</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Consumer Confidence (Mich)</t>
         </is>
@@ -2758,7 +2755,7 @@
           <t>IG_SPREAD</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>IG Credit Spread</t>
         </is>
@@ -2795,7 +2792,7 @@
           <t>HY_SPREAD</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>HY Credit Spread</t>
         </is>
@@ -2832,7 +2829,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
@@ -2869,7 +2866,7 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
@@ -2906,7 +2903,7 @@
           <t>DOW</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Dow Jones</t>
         </is>
@@ -2943,7 +2940,7 @@
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Nasdaq Composite</t>
         </is>
@@ -2980,7 +2977,7 @@
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>FTSE 100</t>
         </is>
@@ -3017,7 +3014,7 @@
           <t>NIKKEI</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Nikkei 225</t>
         </is>
@@ -3054,7 +3051,7 @@
           <t>OIL_WTI</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>WTI Crude Oil</t>
         </is>
@@ -3091,7 +3088,7 @@
           <t>OIL_BRT</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Brent Crude Oil</t>
         </is>
@@ -3128,7 +3125,7 @@
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
@@ -3165,7 +3162,7 @@
           <t>COPPER</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Copper</t>
         </is>
@@ -3202,7 +3199,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>DXY Dollar Index</t>
         </is>
@@ -3239,7 +3236,7 @@
           <t>PUT_CALL</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Put/Call Ratio</t>
         </is>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -74,23 +74,23 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -193,22 +193,22 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-16 15:03 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-16 22:05 UTC</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.020</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.76% ▬ (-2bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.76% ▬ (+0bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -748,17 +748,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.29%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.26%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.30%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.26% ▬ (-4bps). Yield within recent range.</t>
+          <t>10Y yield at 4.29% ▬ (+3bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -790,17 +790,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.87%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.87% ▬ (-3bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.89% ▬ (+2bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -832,32 +832,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.53%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.030</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+          <t>+0.010</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.53% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.54% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -978,12 +978,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1067,7 +1067,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1111,12 +1111,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1200,7 +1200,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$90.32</t>
+          <t>$89.65</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$90.32</t>
+          <t>$89.65</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1242,14 +1242,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $90.32 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $89.65 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$97.98</t>
+          <t>$98.01</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$97.98</t>
+          <t>$98.01</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1284,14 +1284,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $97.98 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $98.01 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,812.10</t>
+          <t>$4,810.90</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,812.10</t>
+          <t>$4,810.90</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,812 ▬ (+0.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,811 ▬ (+0.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.069</t>
+          <t>$6.036</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1368,14 +1368,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.069 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.036 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1417,7 +1417,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.84 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 17.94 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.25</t>
+          <t>98.21</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.25</t>
+          <t>98.21</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.25 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.21 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,028</t>
+          <t>7,041</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,028</t>
+          <t>7,041</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1634,14 +1634,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,028 ▬. Above 50-day SMA (6,764) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,041 ▬. Above 50-day SMA (6,764) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,440</t>
+          <t>48,579</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,440</t>
+          <t>48,579</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,440 ▬.</t>
+          <t>Dow Jones at 48,579 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,031</t>
+          <t>24,103</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,031</t>
+          <t>24,103</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1718,14 +1718,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,031 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,103 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,589</t>
+          <t>10,590</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,589</t>
+          <t>10,590</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,589 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,590 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1797,12 +1797,12 @@
           <t>+1384.102</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>74019.43</t>
+          <t>75065.71</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>74019.43</t>
+          <t>75065.71</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1851,14 +1851,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 74019.43 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 75065.71 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2312.92</t>
+          <t>2348.18</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2312.92</t>
+          <t>2348.18</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2312.92 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2348.18 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 15:03 UTC</t>
+          <t>2026-04-16 22:05 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
@@ -2130,13 +2130,13 @@
         <v>3.76</v>
       </c>
       <c r="D2" s="24" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="E2" s="24" t="n">
-        <v>4.87</v>
+        <v>4.89</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="G2" s="24" t="n">
         <v>3.3202</v>
@@ -2167,43 +2167,43 @@
         <v>285</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7028.3901</v>
+        <v>7041.2798</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>48440.2305</v>
+        <v>48578.7188</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24030.7832</v>
+        <v>24102.7031</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10589.2402</v>
+        <v>10589.9902</v>
       </c>
       <c r="U2" s="24" t="n">
         <v>59518.34</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>18.84</v>
+        <v>17.94</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>90.31999999999999</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>97.98</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4812.1001</v>
+        <v>4810.8999</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.069</v>
+        <v>6.0355</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.255</v>
+        <v>98.20699999999999</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>74019.42969999999</v>
+        <v>75065.71090000001</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2312.9199</v>
+        <v>2348.1799</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-16 22:05 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-17 14:23 UTC</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>3.50–3.75%</t>
+          <t>N/A–3.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Fed Funds at 3.50–3.75% — on hold. Market watching for next pivot signal.</t>
+          <t>Fed Funds at N/A–3.75% — on hold. Market watching for next pivot signal.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$89.65</t>
+          <t>$81.59</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$89.65</t>
+          <t>$81.59</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $89.65 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $81.59 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$98.01</t>
+          <t>$88.71</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$98.01</t>
+          <t>$88.71</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1284,14 +1284,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $98.01 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $88.71 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,810.90</t>
+          <t>$4,885.30</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,810.90</t>
+          <t>$4,885.30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1326,14 +1326,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,811 ▬ (+0.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,885 ▬ (+2.6% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.036</t>
+          <t>$6.093</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.036 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.093 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>286bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>285bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>284bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
           <t>+1.000</t>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 285bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 286bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>17.60</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>17.60</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 17.94 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 17.60 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.21</t>
+          <t>97.80</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.21</t>
+          <t>97.80</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.21 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 97.80 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,041</t>
+          <t>7,114</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,041</t>
+          <t>7,114</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,041 ▬. Above 50-day SMA (6,764) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,114 ▬. Above 50-day SMA (6,769) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,579</t>
+          <t>49,501</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,579</t>
+          <t>49,501</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,579 ▬.</t>
+          <t>Dow Jones at 49,501 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,103</t>
+          <t>24,376</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,103</t>
+          <t>24,376</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,103 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,376 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,590</t>
+          <t>10,646</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,590</t>
+          <t>10,646</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,590 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,646 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>59,518</t>
+          <t>58,476</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>58,134</t>
+          <t>58,476</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+1384.102</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>▲</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,518 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 58,476 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>75065.71</t>
+          <t>77493.00</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>75065.71</t>
+          <t>77493.00</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 75065.71 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 77493.00 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2348.18</t>
+          <t>2434.83</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2348.18</t>
+          <t>2434.83</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2348.18 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2434.83 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16 22:05 UTC</t>
+          <t>2026-04-17 14:23 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
@@ -2164,46 +2164,46 @@
         <v>80</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7041.2798</v>
+        <v>7114.29</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>48578.7188</v>
+        <v>49501.0781</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24102.7031</v>
+        <v>24375.9707</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10589.9902</v>
+        <v>10646.1299</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>59518.34</v>
+        <v>58475.8984</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>17.94</v>
+        <v>17.6</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>89.65000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>98.01000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4810.8999</v>
+        <v>4885.2998</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.0355</v>
+        <v>6.093</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.20699999999999</v>
+        <v>97.798</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>75065.71090000001</v>
+        <v>77493</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2348.1799</v>
+        <v>2434.8301</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-17 14:23 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-17 22:05 UTC</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>N/A–3.75%</t>
+          <t>3.50–3.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Fed Funds at N/A–3.75% — on hold. Market watching for next pivot signal.</t>
+          <t>Fed Funds at 3.50–3.75% — on hold. Market watching for next pivot signal.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.76%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.76%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.76% ▬ (+0bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.78% ▬ (+2bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -748,14 +748,14 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.32%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.29%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.26%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>+0.030</t>
@@ -773,7 +773,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.29% ▬ (+3bps). Yield within recent range.</t>
+          <t>10Y yield at 4.32% ▬ (+3bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -790,17 +790,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.93%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.89%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.87%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.89% ▬ (+2bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.93% ▬ (+4bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -832,14 +832,14 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.53%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
           <t>+0.010</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.54% ▬. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.55% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$81.59</t>
+          <t>$84.00</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$81.59</t>
+          <t>$84.00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $81.59 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $84.00 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$88.71</t>
+          <t>$91.87</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$88.71</t>
+          <t>$91.87</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $88.71 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $91.87 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,885.30</t>
+          <t>$4,849.40</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,885.30</t>
+          <t>$4,849.40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,885 ▬ (+2.6% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,849 ▬ (+1.8% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.093</t>
+          <t>$6.082</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.093 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.082 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>81bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>80bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>81bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>17.60</t>
+          <t>17.48</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>17.60</t>
+          <t>17.48</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 17.60 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 17.48 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>97.80</t>
+          <t>98.23</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>97.80</t>
+          <t>98.23</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 97.80 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.23 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,114</t>
+          <t>7,126</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,114</t>
+          <t>7,126</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,114 ▬. Above 50-day SMA (6,769) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,126 ▬. Above 50-day SMA (6,769) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,501</t>
+          <t>49,447</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,501</t>
+          <t>49,447</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,501 ▬.</t>
+          <t>Dow Jones at 49,447 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,376</t>
+          <t>24,468</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,376</t>
+          <t>24,468</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,376 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,468 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,646</t>
+          <t>10,668</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,646</t>
+          <t>10,668</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,646 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,668 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>58,476</t>
+          <t>59,518</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
+          <t>-1042.440</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 58,476 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 58,476 ▼. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>77493.00</t>
+          <t>77501.24</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>77493.00</t>
+          <t>77501.24</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 77493.00 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 77501.24 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2434.83</t>
+          <t>2431.20</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2434.83</t>
+          <t>2431.20</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2434.83 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2431.20 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,23 +2120,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 14:23 UTC</t>
+          <t>2026-04-17 22:05 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="24" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="D2" s="24" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="E2" s="24" t="n">
-        <v>4.89</v>
+        <v>4.93</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="G2" s="24" t="n">
         <v>3.3202</v>
@@ -2161,49 +2161,49 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P2" s="24" t="n">
         <v>286</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7114.29</v>
+        <v>7126.0601</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>49501.0781</v>
+        <v>49447.4297</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24375.9707</v>
+        <v>24468.4805</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10646.1299</v>
+        <v>10667.6299</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>58475.8984</v>
+        <v>58475.9</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>17.6</v>
+        <v>17.48</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>81.59</v>
+        <v>84</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>88.70999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4885.2998</v>
+        <v>4849.3999</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.093</v>
+        <v>6.0815</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>97.798</v>
+        <v>98.227</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>77493</v>
+        <v>77501.24219999999</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2434.8301</v>
+        <v>2431.2</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-17 22:05 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-20 14:56 UTC</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$86.60</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$86.60</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $84.00 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $86.60 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$91.87</t>
+          <t>$94.75</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$91.87</t>
+          <t>$94.75</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $91.87 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $94.75 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,849.40</t>
+          <t>$4,834.30</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,849.40</t>
+          <t>$4,834.30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,849 ▬ (+1.8% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,834 ▬ (+1.9% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.082</t>
+          <t>$6.062</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.082 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.062 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>80bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>81bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>80bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>-1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>283bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>286bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>285bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>-3.000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 286bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 283bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 17.48 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.35 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.23</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.23</t>
+          <t>98.12</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.23 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.12 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,126</t>
+          <t>7,097</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,126</t>
+          <t>7,097</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,126 ▬. Above 50-day SMA (6,769) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,097 ▬. Above 50-day SMA (6,775) — uptrend intact. -0.4% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,447</t>
+          <t>49,297</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,447</t>
+          <t>49,297</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,447 ▬.</t>
+          <t>Dow Jones at 49,297 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,468</t>
+          <t>24,301</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,468</t>
+          <t>24,301</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,468 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,301 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,668</t>
+          <t>10,609</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,668</t>
+          <t>10,609</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,668 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,609 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>58,476</t>
+          <t>58,825</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,518</t>
+          <t>58,825</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>-1042.440</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 58,476 ▼. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 58,825 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>77501.24</t>
+          <t>75039.55</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>77501.24</t>
+          <t>75039.55</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 77501.24 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 75039.55 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2431.20</t>
+          <t>2290.39</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2431.20</t>
+          <t>2290.39</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2431.20 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2290.39 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-17 22:05 UTC</t>
+          <t>2026-04-20 14:56 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
@@ -2161,49 +2161,49 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="24" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7126.0601</v>
+        <v>7096.96</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>49447.4297</v>
+        <v>49297.1719</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24468.4805</v>
+        <v>24301.2207</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10667.6299</v>
+        <v>10609.1504</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>58475.9</v>
+        <v>58824.8906</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>17.48</v>
+        <v>19.35</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>91.87</v>
+        <v>94.75</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4849.3999</v>
+        <v>4834.2998</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.0815</v>
+        <v>6.0625</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.227</v>
+        <v>98.121</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>77501.24219999999</v>
+        <v>75039.5469</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2431.2</v>
+        <v>2290.3899</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,10 +72,9 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="9"/>
+      <color rgb="0000E676"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -84,9 +83,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="10"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -181,10 +181,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,22 +193,22 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-20 14:56 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-20 22:07 UTC</t>
         </is>
       </c>
     </row>
@@ -706,32 +706,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.71%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.78%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.76%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.020</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▼</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.78% ▬ (+2bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.71% ▼ (-7bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -748,32 +748,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.32%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.29%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.030</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>-0.060</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.32% ▬ (+3bps). Yield within recent range.</t>
+          <t>10Y yield at 4.26% ▼ (-6bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -790,32 +790,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.93%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.89%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.93% ▬ (+4bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.88% ▬ (-5bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -850,14 +850,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.55% ▬. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.54% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -894,7 +894,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -936,12 +936,12 @@
           <t>-11000.000</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -978,12 +978,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1020,12 +1020,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1067,7 +1067,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1111,12 +1111,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1153,12 +1153,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1195,12 +1195,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$86.60</t>
+          <t>$85.89</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$86.60</t>
+          <t>$85.89</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1237,19 +1237,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $86.60 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $85.89 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$94.75</t>
+          <t>$94.28</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$94.75</t>
+          <t>$94.28</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $94.75 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $94.28 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,834.30</t>
+          <t>$4,841.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,834.30</t>
+          <t>$4,841.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1321,19 +1321,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,834 ▬ (+1.9% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,841 ▬ (+2.1% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.062</t>
+          <t>$6.045</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1368,14 +1368,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.062 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.045 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1417,7 +1417,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1454,12 +1454,12 @@
           <t>-3.000</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.87</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.35 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.87 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>98.06</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.12</t>
+          <t>98.06</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1538,19 +1538,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.12 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.06 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,097</t>
+          <t>7,109</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,097</t>
+          <t>7,109</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1634,14 +1634,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,097 ▬. Above 50-day SMA (6,775) — uptrend intact. -0.4% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,109 ▬. Above 50-day SMA (6,775) — uptrend intact. -0.2% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,297</t>
+          <t>49,443</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,297</t>
+          <t>49,443</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1671,19 +1671,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,297 ▬.</t>
+          <t>Dow Jones at 49,443 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,301</t>
+          <t>24,404</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,301</t>
+          <t>24,404</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1718,14 +1718,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,301 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,404 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1755,12 +1755,12 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1789,27 +1789,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>58,825</t>
+          <t>58,476</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
+          <t>+348.992</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 58,825 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 58,825 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>75039.55</t>
+          <t>76147.75</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>75039.55</t>
+          <t>76147.75</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1851,14 +1851,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 75039.55 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76147.75 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2290.39</t>
+          <t>2328.20</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2290.39</t>
+          <t>2328.20</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1888,19 +1888,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2290.39 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2328.20 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,23 +2120,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-20 14:56 UTC</t>
+          <t>2026-04-20 22:07 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="24" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="D2" s="24" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="E2" s="24" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="G2" s="24" t="n">
         <v>3.3202</v>
@@ -2167,43 +2167,43 @@
         <v>283</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7096.96</v>
+        <v>7109.1401</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>49297.1719</v>
+        <v>49442.5586</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24301.2207</v>
+        <v>24404.3926</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10609.1504</v>
+        <v>10609.0801</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>58824.8906</v>
+        <v>58824.89</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>19.35</v>
+        <v>18.87</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>86.59999999999999</v>
+        <v>85.89</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>94.75</v>
+        <v>94.28</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4834.2998</v>
+        <v>4841</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.0625</v>
+        <v>6.0455</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.121</v>
+        <v>98.057</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>75039.5469</v>
+        <v>76147.75</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2290.3899</v>
+        <v>2328.2</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-20 22:07 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-21 14:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$85.89</t>
+          <t>$88.09</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$85.89</t>
+          <t>$88.09</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $85.89 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $88.09 ▬. Moderate level; watching OPEC supply signals.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$94.28</t>
+          <t>$91.37</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$94.28</t>
+          <t>$91.37</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $94.28 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $91.37 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,841.00</t>
+          <t>$4,777.50</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,841.00</t>
+          <t>$4,777.50</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1326,14 +1326,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,841 ▬ (+2.1% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,778 ▬ (-1.0% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.045</t>
+          <t>$6.052</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.045 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.052 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>81bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>80bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>81bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>287bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>283bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>286bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-3.000</t>
+          <t>+4.000</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 283bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 287bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.87 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.09 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.06</t>
+          <t>98.16</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.06</t>
+          <t>98.16</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.06 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.16 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,109</t>
+          <t>7,113</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,109</t>
+          <t>7,113</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,109 ▬. Above 50-day SMA (6,775) — uptrend intact. -0.2% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,113 ▬. Above 50-day SMA (6,779) — uptrend intact. -0.2% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,443</t>
+          <t>49,534</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,443</t>
+          <t>49,534</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,443 ▬.</t>
+          <t>Dow Jones at 49,534 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,404</t>
+          <t>24,452</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,404</t>
+          <t>24,452</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,404 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,452 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,609</t>
+          <t>10,531</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,609</t>
+          <t>10,531</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,609 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,531 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>58,825</t>
+          <t>59,349</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>58,476</t>
+          <t>59,349</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+348.992</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>▲</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 58,825 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,349 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76147.75</t>
+          <t>76190.15</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76147.75</t>
+          <t>76190.15</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76147.75 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76190.15 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2328.20</t>
+          <t>2313.10</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2328.20</t>
+          <t>2313.10</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2328.20 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2313.10 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-20 22:07 UTC</t>
+          <t>2026-04-21 14:51 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
@@ -2161,49 +2161,49 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7109.1401</v>
+        <v>7112.9399</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>49442.5586</v>
+        <v>49534.3789</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24404.3926</v>
+        <v>24451.6406</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10609.0801</v>
+        <v>10531.1396</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>58824.89</v>
+        <v>59349.1719</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>18.87</v>
+        <v>19.09</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>85.89</v>
+        <v>88.09</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>94.28</v>
+        <v>91.37</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4841</v>
+        <v>4777.5</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.0455</v>
+        <v>6.0525</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.057</v>
+        <v>98.16200000000001</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>76147.75</v>
+        <v>76190.14840000001</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2328.2</v>
+        <v>2313.1001</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,6 +72,12 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0000E676"/>
       <sz val="10"/>
@@ -80,12 +86,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
       <sz val="9"/>
     </font>
     <font>
@@ -181,22 +181,25 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,10 +208,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-21 14:51 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-21 22:06 UTC</t>
         </is>
       </c>
     </row>
@@ -706,32 +706,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.72%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.71%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.78%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▼</t>
+          <t>▬</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.71% ▼ (-7bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.72% ▬ (+1bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -753,27 +753,27 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.060</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.26% ▼ (-6bps). Yield within recent range.</t>
+          <t>10Y yield at 4.26% ▬ (+0bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.88% ▬ (-5bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.88% ▬ (+0bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -832,32 +832,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.55%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.010</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.54% ▬. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.52% ▼. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -894,7 +894,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -936,12 +936,12 @@
           <t>-11000.000</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -978,12 +978,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1020,12 +1020,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1111,7 +1111,7 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1153,12 +1153,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1195,7 +1195,7 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$88.09</t>
+          <t>$90.22</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$88.09</t>
+          <t>$90.22</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1237,19 +1237,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $88.09 ▬. Moderate level; watching OPEC supply signals.</t>
+          <t>WTI at $90.22 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$91.37</t>
+          <t>$93.86</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$91.37</t>
+          <t>$93.86</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $91.37 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $93.86 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,777.50</t>
+          <t>$4,738.50</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,777.50</t>
+          <t>$4,738.50</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1321,19 +1321,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,778 ▬ (-1.0% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,738 ▬ (-1.8% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.052</t>
+          <t>$6.017</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1368,14 +1368,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.052 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.017 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1417,7 +1417,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1454,12 +1454,12 @@
           <t>+4.000</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.09 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.50 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.16</t>
+          <t>98.42</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.16</t>
+          <t>98.42</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1538,19 +1538,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.16 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.42 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,113</t>
+          <t>7,064</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,113</t>
+          <t>7,064</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1634,14 +1634,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,113 ▬. Above 50-day SMA (6,779) — uptrend intact. -0.2% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,064 ▬. Above 50-day SMA (6,778) — uptrend intact. -0.9% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,534</t>
+          <t>49,149</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,534</t>
+          <t>49,149</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1671,19 +1671,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,534 ▬.</t>
+          <t>Dow Jones at 49,149 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,452</t>
+          <t>24,260</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,452</t>
+          <t>24,260</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1718,14 +1718,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,452 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,260 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,531</t>
+          <t>10,498</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,531</t>
+          <t>10,498</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1755,19 +1755,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,531 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,498 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,349</t>
+          <t>58,825</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
+          <t>+524.279</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,349 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,349 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76190.15</t>
+          <t>75553.54</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76190.15</t>
+          <t>75553.54</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76190.15 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 75553.54 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2313.10</t>
+          <t>2312.75</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2313.10</t>
+          <t>2312.75</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1888,19 +1888,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2313.10 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2312.75 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,14 +2120,14 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-21 14:51 UTC</t>
+          <t>2026-04-21 22:06 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="24" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="D2" s="24" t="n">
         <v>4.26</v>
@@ -2136,7 +2136,7 @@
         <v>4.88</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="G2" s="24" t="n">
         <v>3.3202</v>
@@ -2167,43 +2167,43 @@
         <v>287</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7112.9399</v>
+        <v>7064.0098</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>49534.3789</v>
+        <v>49149.3789</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24451.6406</v>
+        <v>24259.9648</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10531.1396</v>
+        <v>10498.0898</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>59349.1719</v>
+        <v>59349.17</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>19.09</v>
+        <v>19.5</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>88.09</v>
+        <v>90.22</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>91.37</v>
+        <v>93.86</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4777.5</v>
+        <v>4738.5</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.0525</v>
+        <v>6.017</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.16200000000001</v>
+        <v>98.417</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>76190.14840000001</v>
+        <v>75553.53909999999</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2313.1001</v>
+        <v>2312.75</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -603,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-21 22:06 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-22 14:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$90.22</t>
+          <t>$91.21</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$90.22</t>
+          <t>$91.21</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $90.22 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $91.21 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$93.86</t>
+          <t>$94.95</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$93.86</t>
+          <t>$94.95</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $93.86 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $94.95 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,738.50</t>
+          <t>$4,754.70</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,738.50</t>
+          <t>$4,754.70</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,738 ▬ (-1.8% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,755 ▬ (-0.9% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.017</t>
+          <t>$6.097</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.017 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.097 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>80bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>81bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>80bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>-1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>285bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>287bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>283bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+4.000</t>
+          <t>-2.000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 287bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 285bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.50 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.12 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.42</t>
+          <t>98.41</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.42</t>
+          <t>98.41</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.42 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.41 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,064</t>
+          <t>7,125</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,064</t>
+          <t>7,125</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,064 ▬. Above 50-day SMA (6,778) — uptrend intact. -0.9% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,125 ▬. Above 50-day SMA (6,781) — uptrend intact. -0.0% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,149</t>
+          <t>49,565</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,149</t>
+          <t>49,565</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,149 ▬.</t>
+          <t>Dow Jones at 49,565 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,260</t>
+          <t>24,548</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,260</t>
+          <t>24,548</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,260 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,548 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,498</t>
+          <t>10,485</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,498</t>
+          <t>10,485</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,498 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,485 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>59,349</t>
+          <t>59,586</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>58,825</t>
+          <t>59,586</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+524.279</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>▲</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,349 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,586 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>75553.54</t>
+          <t>78927.60</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>75553.54</t>
+          <t>78927.60</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 75553.54 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78927.60 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2312.75</t>
+          <t>2402.49</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2312.75</t>
+          <t>2402.49</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2312.75 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2402.49 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2120,7 +2120,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>2026-04-21 22:06 UTC</t>
+          <t>2026-04-22 14:51 UTC</t>
         </is>
       </c>
       <c r="B2" s="24" t="n">
@@ -2161,49 +2161,49 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="24" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P2" s="24" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="Q2" s="24" t="n">
-        <v>7064.0098</v>
+        <v>7125.3799</v>
       </c>
       <c r="R2" s="24" t="n">
-        <v>49149.3789</v>
+        <v>49564.8516</v>
       </c>
       <c r="S2" s="24" t="n">
-        <v>24259.9648</v>
+        <v>24547.959</v>
       </c>
       <c r="T2" s="24" t="n">
-        <v>10498.0898</v>
+        <v>10485.2695</v>
       </c>
       <c r="U2" s="24" t="n">
-        <v>59349.17</v>
+        <v>59585.8594</v>
       </c>
       <c r="V2" s="24" t="n">
-        <v>19.5</v>
+        <v>19.12</v>
       </c>
       <c r="W2" s="24" t="n">
-        <v>90.22</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="X2" s="24" t="n">
-        <v>93.86</v>
+        <v>94.95</v>
       </c>
       <c r="Y2" s="24" t="n">
-        <v>4738.5</v>
+        <v>4754.7002</v>
       </c>
       <c r="Z2" s="24" t="n">
-        <v>6.017</v>
+        <v>6.097</v>
       </c>
       <c r="AA2" s="24" t="n">
-        <v>98.417</v>
+        <v>98.411</v>
       </c>
       <c r="AB2" s="24" t="n">
-        <v>75553.53909999999</v>
+        <v>78927.60159999999</v>
       </c>
       <c r="AC2" s="24" t="n">
-        <v>2312.75</v>
+        <v>2402.49</v>
       </c>
       <c r="AD2" s="24" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,15 +72,15 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF4D4D"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -90,7 +90,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -181,34 +181,37 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-22 14:51 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-22 22:09 UTC</t>
         </is>
       </c>
     </row>
@@ -706,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.72%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.71%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.72% ▬ (+1bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.78% ▲ (+6bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -748,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.26%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.26%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -766,14 +769,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.26% ▬ (+0bps). Yield within recent range.</t>
+          <t>10Y yield at 4.30% ▬ (+4bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -790,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.88%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>+0.010</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.88% ▬ (+0bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.89% ▬ (+1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -832,22 +835,22 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.52%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
@@ -857,7 +860,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.52% ▼. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -894,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -936,12 +939,12 @@
           <t>-11000.000</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -978,7 +981,7 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1020,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1067,7 +1070,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1111,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1153,12 +1156,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1195,12 +1198,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1224,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$91.21</t>
+          <t>$92.87</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$91.21</t>
+          <t>$92.87</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1237,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $91.21 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $92.87 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1266,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$94.95</t>
+          <t>$101.85</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$94.95</t>
+          <t>$101.85</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1284,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $94.95 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $101.85 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1308,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,754.70</t>
+          <t>$4,758.30</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,754.70</t>
+          <t>$4,758.30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1321,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,755 ▬ (-0.9% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,758 ▬ (-0.9% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1350,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.097</t>
+          <t>$6.137</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1375,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.097 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.137 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1454,12 +1457,12 @@
           <t>-2.000</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1483,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1508,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.12 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.92 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1525,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.41</t>
+          <t>98.60</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.41</t>
+          <t>98.60</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1538,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.41 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.60 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1616,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,125</t>
+          <t>7,138</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,125</t>
+          <t>7,138</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1641,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,125 ▬. Above 50-day SMA (6,781) — uptrend intact. -0.0% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,138 ▬. Above 50-day SMA (6,781) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1658,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,565</t>
+          <t>49,490</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,565</t>
+          <t>49,490</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1671,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,565 ▬.</t>
+          <t>Dow Jones at 49,490 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1700,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,548</t>
+          <t>24,658</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,548</t>
+          <t>24,658</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1725,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,548 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,658 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1742,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,485</t>
+          <t>10,476</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,485</t>
+          <t>10,476</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1755,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,485 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,476 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1789,17 +1792,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,586</t>
+          <t>59,349</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
+          <t>+236.688</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>▲</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1809,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,586 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,586 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1833,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>78927.60</t>
+          <t>78849.52</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>78927.60</t>
+          <t>78849.52</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1851,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 78927.60 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78849.52 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1875,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2402.49</t>
+          <t>2405.69</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2402.49</t>
+          <t>2405.69</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1888,19 +1891,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2402.49 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2405.69 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2118,94 +2121,94 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>2026-04-22 14:51 UTC</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:09 UTC</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
-      <c r="C2" s="24" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="D2" s="24" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="E2" s="24" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="F2" s="24" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G2" s="24" t="n">
+      <c r="C2" s="25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="D2" s="25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E2" s="25" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="F2" s="25" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G2" s="25" t="n">
         <v>3.3202</v>
       </c>
-      <c r="H2" s="24" t="n">
+      <c r="H2" s="25" t="n">
         <v>2.6731</v>
       </c>
-      <c r="I2" s="24" t="n">
+      <c r="I2" s="25" t="n">
         <v>2.9678</v>
       </c>
-      <c r="J2" s="24" t="n">
+      <c r="J2" s="25" t="n">
         <v>4.3</v>
       </c>
-      <c r="K2" s="24" t="n">
+      <c r="K2" s="25" t="n">
         <v>207000</v>
       </c>
-      <c r="L2" s="24" t="n">
+      <c r="L2" s="25" t="n">
         <v>178</v>
       </c>
-      <c r="M2" s="24" t="n"/>
-      <c r="N2" s="24" t="n">
+      <c r="M2" s="25" t="n"/>
+      <c r="N2" s="25" t="n">
         <v>56.6</v>
       </c>
-      <c r="O2" s="24" t="n">
+      <c r="O2" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="P2" s="24" t="n">
+      <c r="P2" s="25" t="n">
         <v>285</v>
       </c>
-      <c r="Q2" s="24" t="n">
-        <v>7125.3799</v>
-      </c>
-      <c r="R2" s="24" t="n">
-        <v>49564.8516</v>
-      </c>
-      <c r="S2" s="24" t="n">
-        <v>24547.959</v>
-      </c>
-      <c r="T2" s="24" t="n">
-        <v>10485.2695</v>
-      </c>
-      <c r="U2" s="24" t="n">
-        <v>59585.8594</v>
-      </c>
-      <c r="V2" s="24" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="W2" s="24" t="n">
-        <v>91.20999999999999</v>
-      </c>
-      <c r="X2" s="24" t="n">
-        <v>94.95</v>
-      </c>
-      <c r="Y2" s="24" t="n">
-        <v>4754.7002</v>
-      </c>
-      <c r="Z2" s="24" t="n">
-        <v>6.097</v>
-      </c>
-      <c r="AA2" s="24" t="n">
-        <v>98.411</v>
-      </c>
-      <c r="AB2" s="24" t="n">
-        <v>78927.60159999999</v>
-      </c>
-      <c r="AC2" s="24" t="n">
-        <v>2402.49</v>
-      </c>
-      <c r="AD2" s="24" t="n"/>
+      <c r="Q2" s="25" t="n">
+        <v>7137.8999</v>
+      </c>
+      <c r="R2" s="25" t="n">
+        <v>49490.0312</v>
+      </c>
+      <c r="S2" s="25" t="n">
+        <v>24657.5664</v>
+      </c>
+      <c r="T2" s="25" t="n">
+        <v>10476.46</v>
+      </c>
+      <c r="U2" s="25" t="n">
+        <v>59585.86</v>
+      </c>
+      <c r="V2" s="25" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="W2" s="25" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="X2" s="25" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="Y2" s="25" t="n">
+        <v>4758.2998</v>
+      </c>
+      <c r="Z2" s="25" t="n">
+        <v>6.137</v>
+      </c>
+      <c r="AA2" s="25" t="n">
+        <v>98.599</v>
+      </c>
+      <c r="AB2" s="25" t="n">
+        <v>78849.52340000001</v>
+      </c>
+      <c r="AC2" s="25" t="n">
+        <v>2405.6899</v>
+      </c>
+      <c r="AD2" s="25" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2274,7 +2277,7 @@
           <t>FED_FUNDS</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Fed Funds Rate</t>
         </is>
@@ -2311,7 +2314,7 @@
           <t>US_2Y</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>US 2Y Treasury</t>
         </is>
@@ -2348,7 +2351,7 @@
           <t>US_10Y</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>US 10Y Treasury</t>
         </is>
@@ -2385,7 +2388,7 @@
           <t>US_30Y</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>US 30Y Treasury</t>
         </is>
@@ -2422,7 +2425,7 @@
           <t>SPREAD_2S10S</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>2s10s Yield Spread</t>
         </is>
@@ -2459,7 +2462,7 @@
           <t>CPI_YOY</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>CPI YoY</t>
         </is>
@@ -2496,7 +2499,7 @@
           <t>CORE_CPI_YOY</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Core CPI YoY</t>
         </is>
@@ -2533,7 +2536,7 @@
           <t>CORE_PCE_YOY</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Core PCE YoY</t>
         </is>
@@ -2570,7 +2573,7 @@
           <t>UNEMPLOYMENT</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Unemployment Rate</t>
         </is>
@@ -2607,7 +2610,7 @@
           <t>INITIAL_CLAIMS</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Initial Jobless Claims</t>
         </is>
@@ -2644,7 +2647,7 @@
           <t>NFP</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Nonfarm Payrolls MoM</t>
         </is>
@@ -2681,7 +2684,7 @@
           <t>ISM_MFG</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>ISM Manufacturing PMI</t>
         </is>
@@ -2718,7 +2721,7 @@
           <t>CONSUMER_CONF</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Consumer Confidence (Mich)</t>
         </is>
@@ -2755,7 +2758,7 @@
           <t>IG_SPREAD</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>IG Credit Spread</t>
         </is>
@@ -2792,7 +2795,7 @@
           <t>HY_SPREAD</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>HY Credit Spread</t>
         </is>
@@ -2829,7 +2832,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
@@ -2866,7 +2869,7 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
@@ -2903,7 +2906,7 @@
           <t>DOW</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Dow Jones</t>
         </is>
@@ -2940,7 +2943,7 @@
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Nasdaq Composite</t>
         </is>
@@ -2977,7 +2980,7 @@
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>FTSE 100</t>
         </is>
@@ -3014,7 +3017,7 @@
           <t>NIKKEI</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Nikkei 225</t>
         </is>
@@ -3051,7 +3054,7 @@
           <t>OIL_WTI</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>WTI Crude Oil</t>
         </is>
@@ -3088,7 +3091,7 @@
           <t>OIL_BRT</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Brent Crude Oil</t>
         </is>
@@ -3125,7 +3128,7 @@
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
@@ -3162,7 +3165,7 @@
           <t>COPPER</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Copper</t>
         </is>
@@ -3199,7 +3202,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>DXY Dollar Index</t>
         </is>
@@ -3236,7 +3239,7 @@
           <t>PUT_CALL</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Put/Call Ratio</t>
         </is>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -202,9 +202,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -212,6 +209,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-22 22:09 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-23 15:19 UTC</t>
         </is>
       </c>
     </row>
@@ -926,32 +926,32 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>214K</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>208K</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>-11000.000</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+          <t>+6000.000</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Initial claims at 207K ▼. Sub-220K — historically tight labor market.</t>
+          <t>Initial claims at 214K ▲. Sub-220K — historically tight labor market.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -981,7 +981,7 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1028,7 +1028,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1114,7 +1114,7 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1156,12 +1156,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$92.87</t>
+          <t>$93.68</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$92.87</t>
+          <t>$93.68</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $92.87 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $93.68 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$101.85</t>
+          <t>$103.03</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$101.85</t>
+          <t>$103.03</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $101.85 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $103.03 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,758.30</t>
+          <t>$4,745.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,758.30</t>
+          <t>$4,745.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1329,14 +1329,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,758 ▬ (-0.9% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,746 ▬ (-0.8% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.137</t>
+          <t>$6.098</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.137 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.098 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,14 +1402,14 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>79bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>80bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>81bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
           <t>-1.000</t>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 79bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>284bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>285bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>287bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-2.000</t>
+          <t>-1.000</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
@@ -1462,14 +1462,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 285bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 284bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.92 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.83 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.60</t>
+          <t>98.61</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.60</t>
+          <t>98.61</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.60 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.61 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,138</t>
+          <t>7,145</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,138</t>
+          <t>7,145</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,138 ▬. Above 50-day SMA (6,781) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,145 ▬. Above 50-day SMA (6,786) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,490</t>
+          <t>49,453</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,490</t>
+          <t>49,453</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,490 ▬.</t>
+          <t>Dow Jones at 49,453 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,658</t>
+          <t>24,656</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,658</t>
+          <t>24,656</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,658 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,656 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,476</t>
+          <t>10,464</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,476</t>
+          <t>10,464</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,476 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,464 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>59,140</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>59,586</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>59,349</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+236.688</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>▲</t>
+          <t>-445.629</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,586 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,140 ▼. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>78849.52</t>
+          <t>78511.37</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>78849.52</t>
+          <t>78511.37</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 78849.52 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78511.37 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2405.69</t>
+          <t>2340.63</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2405.69</t>
+          <t>2340.63</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2405.69 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2340.63 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-22 22:09 UTC</t>
+          <t>2026-04-23 15:19 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2154,7 +2154,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" s="25" t="n">
-        <v>207000</v>
+        <v>214000</v>
       </c>
       <c r="L2" s="25" t="n">
         <v>178</v>
@@ -2164,49 +2164,49 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7137.8999</v>
+        <v>7145.3901</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49490.0312</v>
+        <v>49452.8711</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24657.5664</v>
+        <v>24655.5488</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10476.46</v>
+        <v>10464.2197</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59585.86</v>
+        <v>59140.23</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.92</v>
+        <v>18.83</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>92.87</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>101.85</v>
+        <v>103.03</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4758.2998</v>
+        <v>4745.6001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.137</v>
+        <v>6.0985</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.599</v>
+        <v>98.61199999999999</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>78849.52340000001</v>
+        <v>78511.36719999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2405.6899</v>
+        <v>2340.6299</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,11 +72,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF4D4D"/>
@@ -91,6 +86,11 @@
     <font>
       <b val="1"/>
       <color rgb="0000E676"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -181,37 +181,37 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-23 15:19 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-23 22:06 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.78%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.72%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>▬</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.78% ▲ (+6bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.79% ▬ (+1bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -769,14 +769,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.30% ▬ (+4bps). Yield within recent range.</t>
+          <t>10Y yield at 4.30% ▬ (+0bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.90%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.89%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
           <t>+0.010</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.89% ▬ (+1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.90% ▬ (+1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -853,7 +853,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,7 +939,7 @@
           <t>+6000.000</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -986,7 +986,7 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1070,7 +1070,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1119,7 +1119,7 @@
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,12 +1198,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$93.68</t>
+          <t>$97.00</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$93.68</t>
+          <t>$97.00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $93.68 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $97.00 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$103.03</t>
+          <t>$106.47</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$103.03</t>
+          <t>$106.47</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $103.03 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $106.47 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,745.60</t>
+          <t>$4,708.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,745.60</t>
+          <t>$4,708.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,746 ▬ (-0.8% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,709 ▬ (-1.6% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.098</t>
+          <t>$6.025</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.098 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.025 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1457,7 +1457,7 @@
           <t>-1.000</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.83 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 19.31 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.61</t>
+          <t>98.81</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.61</t>
+          <t>98.81</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,7 +1541,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.61 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.81 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,145</t>
+          <t>7,108</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,145</t>
+          <t>7,108</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,145 ▬. Above 50-day SMA (6,786) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,108 ▬. Above 50-day SMA (6,785) — uptrend intact. -0.4% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,453</t>
+          <t>49,310</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,453</t>
+          <t>49,310</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,7 +1674,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,453 ▬.</t>
+          <t>Dow Jones at 49,310 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,656</t>
+          <t>24,439</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,656</t>
+          <t>24,439</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,656 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,439 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,464</t>
+          <t>10,457</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,464</t>
+          <t>10,457</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,7 +1758,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,464 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,457 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1800,12 +1800,12 @@
           <t>-445.629</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>78511.37</t>
+          <t>78061.10</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>78511.37</t>
+          <t>78061.10</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 78511.37 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78061.10 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2340.63</t>
+          <t>2328.33</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2340.63</t>
+          <t>2328.33</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1891,19 +1891,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2340.63 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2328.33 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,20 +2123,20 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-23 15:19 UTC</t>
+          <t>2026-04-23 22:06 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="D2" s="25" t="n">
         <v>4.3</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>0.51</v>
@@ -2170,43 +2170,43 @@
         <v>284</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7145.3901</v>
+        <v>7108.3999</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49452.8711</v>
+        <v>49310.3203</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24655.5488</v>
+        <v>24438.5039</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10464.2197</v>
+        <v>10457.0098</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>59140.23</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.83</v>
+        <v>19.31</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>93.68000000000001</v>
+        <v>97</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>103.03</v>
+        <v>106.47</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4745.6001</v>
+        <v>4708.6001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0985</v>
+        <v>6.025</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.61199999999999</v>
+        <v>98.80800000000001</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>78511.36719999999</v>
+        <v>78061.10159999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2340.6299</v>
+        <v>2328.3301</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-23 22:06 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-24 14:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$97.00</t>
+          <t>$95.08</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$97.00</t>
+          <t>$95.08</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $97.00 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $95.08 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$106.47</t>
+          <t>$98.91</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$106.47</t>
+          <t>$98.91</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $106.47 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $98.91 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,708.60</t>
+          <t>$4,744.30</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,708.60</t>
+          <t>$4,744.30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,709 ▬ (-1.6% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,744 ▬ (-2.3% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.025</t>
+          <t>$6.027</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.025 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.027 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>80bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>79bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>80bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 79bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>286bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>284bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>285bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-1.000</t>
+          <t>+2.000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 284bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 286bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 19.31 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.93 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.81</t>
+          <t>98.59</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.81</t>
+          <t>98.59</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.81 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.59 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,108</t>
+          <t>7,133</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,108</t>
+          <t>7,133</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,108 ▬. Above 50-day SMA (6,785) — uptrend intact. -0.4% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,133 ▬. Above 50-day SMA (6,789) — uptrend intact. -0.1% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,310</t>
+          <t>49,163</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,310</t>
+          <t>49,163</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,310 ▬.</t>
+          <t>Dow Jones at 49,163 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,439</t>
+          <t>24,643</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,439</t>
+          <t>24,643</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,439 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,643 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,457</t>
+          <t>10,406</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,457</t>
+          <t>10,406</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,457 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,406 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>59,140</t>
+          <t>59,716</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,586</t>
+          <t>59,716</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>-445.629</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,140 ▼. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,716 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>78061.10</t>
+          <t>78004.81</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>78061.10</t>
+          <t>78004.81</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 78061.10 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78004.81 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2328.33</t>
+          <t>2314.62</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2328.33</t>
+          <t>2314.62</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2328.33 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2314.62 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-23 22:06 UTC</t>
+          <t>2026-04-24 14:47 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2164,49 +2164,49 @@
         <v>56.6</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7108.3999</v>
+        <v>7133.1001</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49310.3203</v>
+        <v>49162.5508</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24438.5039</v>
+        <v>24643.4922</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10457.0098</v>
+        <v>10406.4902</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59140.23</v>
+        <v>59716.1797</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>19.31</v>
+        <v>18.93</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>97</v>
+        <v>95.08</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>106.47</v>
+        <v>98.91</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4708.6001</v>
+        <v>4744.2998</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.025</v>
+        <v>6.0265</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.80800000000001</v>
+        <v>98.59</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>78061.10159999999</v>
+        <v>78004.8125</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2328.3301</v>
+        <v>2314.6201</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -78,6 +78,11 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
@@ -86,11 +91,6 @@
     <font>
       <b val="1"/>
       <color rgb="0000E676"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -184,13 +184,13 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -199,19 +199,19 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-24 14:47 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-24 22:06 UTC</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.83%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.79%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.78%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.79% ▬ (+1bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.83% ▬ (+4bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.30%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.30%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -769,14 +769,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.30% ▬ (+0bps). Yield within recent range.</t>
+          <t>10Y yield at 4.34% ▬ (+4bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.92%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.90%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.89%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>+0.020</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -811,14 +811,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.90% ▬ (+1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.92% ▬ (+2bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.51%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+          <t>+0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.53% ▲. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+6000.000</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1028,7 +1028,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1052,32 +1052,32 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>53.30</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>56.60</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>56.40</t>
-        </is>
-      </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>+0.200</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+          <t>-3.300</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Consumer confidence at 56.6 ▬. Below 80 — significant pessimism; spending headwinds.</t>
+          <t>Consumer confidence at 53.3 ▼. Below 80 — significant pessimism; spending headwinds.</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1114,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,12 +1198,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$95.08</t>
+          <t>$94.88</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$95.08</t>
+          <t>$94.88</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1245,14 +1245,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $95.08 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $94.88 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$98.91</t>
+          <t>$99.78</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$98.91</t>
+          <t>$99.78</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $98.91 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $99.78 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,744.30</t>
+          <t>$4,725.40</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,744.30</t>
+          <t>$4,725.40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1329,14 +1329,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,744 ▬ (-2.3% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,725 ▬ (-2.7% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.027</t>
+          <t>$6.029</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.027 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.029 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1462,7 +1462,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.71</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.93 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.71 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.59</t>
+          <t>98.51</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.59</t>
+          <t>98.51</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.59 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.51 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,133</t>
+          <t>7,165</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,133</t>
+          <t>7,165</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,133 ▬. Above 50-day SMA (6,789) — uptrend intact. -0.1% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,165 ▬. Above 50-day SMA (6,789) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,163</t>
+          <t>49,231</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,163</t>
+          <t>49,231</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,163 ▬.</t>
+          <t>Dow Jones at 49,231 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,643</t>
+          <t>24,837</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,643</t>
+          <t>24,837</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,643 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,837 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,406</t>
+          <t>10,379</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,406</t>
+          <t>10,379</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,406 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,379 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,716</t>
+          <t>59,140</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
+          <t>+575.950</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,716 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,716 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>78004.81</t>
+          <t>77599.58</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>78004.81</t>
+          <t>77599.58</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 78004.81 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 77599.58 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2314.62</t>
+          <t>2314.58</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2314.62</t>
+          <t>2314.58</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1896,14 +1896,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2314.62 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2314.58 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,23 +2123,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-24 14:47 UTC</t>
+          <t>2026-04-24 22:06 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.9</v>
+        <v>4.92</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="M2" s="25" t="n"/>
       <c r="N2" s="25" t="n">
-        <v>56.6</v>
+        <v>53.3</v>
       </c>
       <c r="O2" s="25" t="n">
         <v>80</v>
@@ -2170,43 +2170,43 @@
         <v>286</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7133.1001</v>
+        <v>7165.0801</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49162.5508</v>
+        <v>49230.7109</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24643.4922</v>
+        <v>24836.5977</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10406.4902</v>
+        <v>10379.0801</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59716.1797</v>
+        <v>59716.18</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.93</v>
+        <v>18.71</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>95.08</v>
+        <v>94.88</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>98.91</v>
+        <v>99.78</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4744.2998</v>
+        <v>4725.3999</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0265</v>
+        <v>6.0285</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.59</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>78004.8125</v>
+        <v>77599.5781</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2314.6201</v>
+        <v>2314.5801</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-24 22:06 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-27 15:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$94.88</t>
+          <t>$96.93</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$94.88</t>
+          <t>$96.93</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $94.88 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $96.93 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$99.78</t>
+          <t>$101.88</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$99.78</t>
+          <t>$101.88</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $99.78 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $101.88 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,725.40</t>
+          <t>$4,691.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,725.40</t>
+          <t>$4,691.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,725 ▬ (-2.7% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,691 ▬ (-2.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.029</t>
+          <t>$6.068</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.029 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.068 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>79bps</t>
+          <t>80bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>284bps</t>
+          <t>286bps</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+2.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.71</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.71 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.63 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.51</t>
+          <t>98.36</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.51</t>
+          <t>98.36</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.51 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.36 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,165</t>
+          <t>7,153</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,165</t>
+          <t>7,153</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,165 ▬. Above 50-day SMA (6,789) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,153 ▬. Above 50-day SMA (6,796) — uptrend intact. -0.2% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,231</t>
+          <t>49,052</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,231</t>
+          <t>49,052</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,231 ▬.</t>
+          <t>Dow Jones at 49,052 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,837</t>
+          <t>24,762</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,837</t>
+          <t>24,762</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,837 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,762 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,379</t>
+          <t>10,335</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,379</t>
+          <t>10,335</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,379 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,335 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>60,537</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>59,716</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>59,140</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+575.950</t>
+          <t>+821.180</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,716 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 60,537 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>77599.58</t>
+          <t>77504.04</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>77599.58</t>
+          <t>77504.04</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 77599.58 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 77504.04 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2314.58</t>
+          <t>2299.76</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2314.58</t>
+          <t>2299.76</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2314.58 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2299.76 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-24 22:06 UTC</t>
+          <t>2026-04-27 15:11 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2170,43 +2170,43 @@
         <v>286</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7165.0801</v>
+        <v>7153.4199</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49230.7109</v>
+        <v>49052.1094</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24836.5977</v>
+        <v>24761.793</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10379.0801</v>
+        <v>10335.46</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59716.18</v>
+        <v>60537.36</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.71</v>
+        <v>18.63</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>94.88</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>99.78</v>
+        <v>101.88</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4725.3999</v>
+        <v>4691</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0285</v>
+        <v>6.0675</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.51000000000001</v>
+        <v>98.358</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>77599.5781</v>
+        <v>77504.03909999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2314.5801</v>
+        <v>2299.76</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,14 +72,8 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
+      <color rgb="0000E676"/>
       <sz val="10"/>
     </font>
     <font>
@@ -89,8 +83,14 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -181,37 +181,37 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-27 15:11 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-27 22:12 UTC</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>3.50–3.75%</t>
+          <t>N/A–3.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Fed Funds at 3.50–3.75% — on hold. Market watching for next pivot signal.</t>
+          <t>Fed Funds at N/A–3.75% — on hold. Market watching for next pivot signal.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -709,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.83%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.79%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▼</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.83% ▬ (+4bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.78% ▼ (-5bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.31%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.34%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.30%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>-0.030</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.34% ▬ (+4bps). Yield within recent range.</t>
+          <t>10Y yield at 4.31% ▬ (-3bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.92%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.020</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.92% ▬ (+2bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.91% ▬ (-1bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.53%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
+          <t>+0.040</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.53% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.57% ▲. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+6000.000</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1023,7 +1023,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1065,12 +1065,12 @@
           <t>-3.300</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1156,7 +1156,7 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -1198,12 +1198,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$96.93</t>
+          <t>$96.57</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$96.93</t>
+          <t>$96.57</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $96.93 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $96.57 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$101.88</t>
+          <t>$101.72</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$101.88</t>
+          <t>$101.72</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $101.88 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $101.72 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,691.00</t>
+          <t>$4,698.20</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,691.00</t>
+          <t>$4,698.20</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,7 +1324,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,691 ▬ (-2.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,698 ▬ (-2.3% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.068</t>
+          <t>$6.083</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.068 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.083 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1457,12 +1457,12 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.63 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.02 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.36</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.36</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.36 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.48 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,153</t>
+          <t>7,174</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,153</t>
+          <t>7,174</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,153 ▬. Above 50-day SMA (6,796) — uptrend intact. -0.2% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,174 ▬. Above 50-day SMA (6,796) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,052</t>
+          <t>49,168</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,052</t>
+          <t>49,168</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,052 ▬.</t>
+          <t>Dow Jones at 49,168 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,762</t>
+          <t>24,887</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,762</t>
+          <t>24,887</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,762 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,887 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,335</t>
+          <t>10,321</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,335</t>
+          <t>10,321</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,7 +1758,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,335 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,321 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1800,12 +1800,12 @@
           <t>+821.180</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>77504.04</t>
+          <t>76844.60</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>77504.04</t>
+          <t>76844.60</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 77504.04 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76844.60 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2299.76</t>
+          <t>2288.06</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2299.76</t>
+          <t>2288.06</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1891,19 +1891,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2299.76 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2288.06 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,23 +2123,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-27 15:11 UTC</t>
+          <t>2026-04-27 22:12 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2170,43 +2170,43 @@
         <v>286</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7153.4199</v>
+        <v>7173.9102</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49052.1094</v>
+        <v>49167.7891</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24761.793</v>
+        <v>24887.0996</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10335.46</v>
+        <v>10321.0898</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>60537.36</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.63</v>
+        <v>18.02</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>96.93000000000001</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>101.88</v>
+        <v>101.72</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4691</v>
+        <v>4698.2002</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0675</v>
+        <v>6.083</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.358</v>
+        <v>98.48099999999999</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>77504.03909999999</v>
+        <v>76844.60159999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2299.76</v>
+        <v>2288.0601</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-27 22:12 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-28 15:31 UTC</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>N/A–3.75%</t>
+          <t>3.50–3.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Fed Funds at N/A–3.75% — on hold. Market watching for next pivot signal.</t>
+          <t>Fed Funds at 3.50–3.75% — on hold. Market watching for next pivot signal.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$96.57</t>
+          <t>$99.55</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$96.57</t>
+          <t>$99.55</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $96.57 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $99.55 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$101.72</t>
+          <t>$104.08</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$101.72</t>
+          <t>$104.08</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $101.72 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $104.08 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,698.20</t>
+          <t>$4,583.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,698.20</t>
+          <t>$4,583.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,698 ▬ (-2.3% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,584 ▬ (-2.4% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.083</t>
+          <t>$5.971</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.083 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.971 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.44</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.44</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.02 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.44 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>98.67</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>98.67</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.48 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.67 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,174</t>
+          <t>7,119</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,174</t>
+          <t>7,119</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,174 ▬. Above 50-day SMA (6,796) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,119 ▬. Above 50-day SMA (6,802) — uptrend intact. -0.8% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,168</t>
+          <t>49,213</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,168</t>
+          <t>49,213</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,168 ▬.</t>
+          <t>Dow Jones at 49,213 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,887</t>
+          <t>24,542</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,887</t>
+          <t>24,542</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,887 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,542 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,321</t>
+          <t>10,329</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,321</t>
+          <t>10,329</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,321 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,329 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>59,917</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>60,537</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>59,716</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+821.180</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>▲</t>
+          <t>-619.899</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 60,537 ▲. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,917 ▼. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76844.60</t>
+          <t>75933.91</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76844.60</t>
+          <t>75933.91</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76844.60 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 75933.91 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2288.06</t>
+          <t>2270.88</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2288.06</t>
+          <t>2270.88</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2288.06 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2270.88 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-27 22:12 UTC</t>
+          <t>2026-04-28 15:31 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2170,43 +2170,43 @@
         <v>286</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7173.9102</v>
+        <v>7119.1499</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49167.7891</v>
+        <v>49213.2891</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24887.0996</v>
+        <v>24541.6855</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10321.0898</v>
+        <v>10329.3203</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>60537.36</v>
+        <v>59917.46</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.02</v>
+        <v>18.44</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>96.56999999999999</v>
+        <v>99.55</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>101.72</v>
+        <v>104.08</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4698.2002</v>
+        <v>4583.6001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.083</v>
+        <v>5.971</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.48099999999999</v>
+        <v>98.672</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>76844.60159999999</v>
+        <v>75933.9062</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2288.0601</v>
+        <v>2270.8799</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-28 15:31 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-28 22:30 UTC</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>3.50–3.75%</t>
+          <t>N/A–3.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Fed Funds at 3.50–3.75% — on hold. Market watching for next pivot signal.</t>
+          <t>Fed Funds at N/A–3.75% — on hold. Market watching for next pivot signal.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.94%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.91%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.92%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>+0.030</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.91% ▬ (-1bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.94% ▬ (+3bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$99.55</t>
+          <t>$99.36</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$99.55</t>
+          <t>$99.36</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $99.55 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $99.36 ▬. Elevated — headwind for inflation and consumer spending.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$104.08</t>
+          <t>$103.90</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$104.08</t>
+          <t>$103.90</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $104.08 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $103.90 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,583.60</t>
+          <t>$4,610.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,583.60</t>
+          <t>$4,610.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,584 ▬ (-2.4% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,611 ▬ (-1.9% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.971</t>
+          <t>$5.978</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.971 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.978 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>81bps</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>80bps</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>80bps</t>
-        </is>
-      </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IG spread at 80bps ▬. Tight — benign credit environment.</t>
+          <t>IG spread at 81bps ▬. Tight — benign credit environment.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>284bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>286bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>286bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>-2.000</t>
         </is>
       </c>
       <c r="E25" s="17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 286bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 284bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.44 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 17.83 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.67</t>
+          <t>98.60</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.67</t>
+          <t>98.60</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.67 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.60 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,119</t>
+          <t>7,139</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,119</t>
+          <t>7,139</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,119 ▬. Above 50-day SMA (6,802) — uptrend intact. -0.8% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,139 ▬. Above 50-day SMA (6,802) — uptrend intact. -0.5% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,213</t>
+          <t>49,142</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,213</t>
+          <t>49,142</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,213 ▬.</t>
+          <t>Dow Jones at 49,142 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,542</t>
+          <t>24,664</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,542</t>
+          <t>24,664</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,542 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,664 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,329</t>
+          <t>10,333</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,329</t>
+          <t>10,333</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,329 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,333 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>75933.91</t>
+          <t>76337.04</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>75933.91</t>
+          <t>76337.04</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 75933.91 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76337.04 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2270.88</t>
+          <t>2289.71</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2270.88</t>
+          <t>2289.71</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2270.88 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2289.71 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-28 15:31 UTC</t>
+          <t>2026-04-28 22:30 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2136,7 +2136,7 @@
         <v>4.31</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="F2" s="25" t="n">
         <v>0.57</v>
@@ -2164,49 +2164,49 @@
         <v>53.3</v>
       </c>
       <c r="O2" s="25" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7119.1499</v>
+        <v>7138.7998</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49213.2891</v>
+        <v>49141.9297</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24541.6855</v>
+        <v>24663.7988</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10329.3203</v>
+        <v>10332.79</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>59917.46</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.44</v>
+        <v>17.83</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>99.55</v>
+        <v>99.36</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>104.08</v>
+        <v>103.9</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4583.6001</v>
+        <v>4610.6001</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.971</v>
+        <v>5.978</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.672</v>
+        <v>98.595</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>75933.9062</v>
+        <v>76337.03909999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2270.8799</v>
+        <v>2289.71</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,6 +72,12 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0000E676"/>
       <sz val="10"/>
@@ -80,12 +86,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
       <sz val="9"/>
     </font>
     <font>
@@ -181,19 +181,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,16 +211,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-28 22:30 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-29 15:22 UTC</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>N/A–3.75%</t>
+          <t>3.50–3.75%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>Fed Funds at N/A–3.75% — on hold. Market watching for next pivot signal.</t>
+          <t>Fed Funds at 3.50–3.75% — on hold. Market watching for next pivot signal.</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▼</t>
+          <t>▬</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.78% ▼ (-5bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.78% ▬ (+0bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.35%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.31%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.34%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>+0.040</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.31% ▬ (-3bps). Yield within recent range.</t>
+          <t>10Y yield at 4.35% ▬ (+4bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -806,12 +806,12 @@
           <t>+0.030</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.57%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.53%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.040</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.57% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.52% ▼. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+6000.000</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1065,12 +1065,12 @@
           <t>-3.300</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1156,12 +1156,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,12 +1198,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$99.36</t>
+          <t>$105.31</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$99.36</t>
+          <t>$105.31</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $99.36 ▬. Elevated — headwind for inflation and consumer spending.</t>
+          <t>WTI at $105.31 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$103.90</t>
+          <t>$109.83</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$103.90</t>
+          <t>$109.83</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $103.90 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $109.83 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,610.60</t>
+          <t>$4,550.80</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,610.60</t>
+          <t>$4,550.80</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,611 ▬ (-1.9% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,551 ▬ (-3.8% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.978</t>
+          <t>$5.947</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.978 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.947 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>80bps</t>
+          <t>81bps</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>+0.000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1444,32 +1444,32 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>285bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>284bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>286bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-2.000</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
+          <t>+1.000</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 284bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 285bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>18.20</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 17.83 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.20 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.60</t>
+          <t>98.81</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.60</t>
+          <t>98.81</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.60 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.81 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,139</t>
+          <t>7,131</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,139</t>
+          <t>7,131</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,139 ▬. Above 50-day SMA (6,802) — uptrend intact. -0.5% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,131 ▬. Above 50-day SMA (6,808) — uptrend intact. -0.6% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,142</t>
+          <t>48,865</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,142</t>
+          <t>48,865</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,142 ▬.</t>
+          <t>Dow Jones at 48,865 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,664</t>
+          <t>24,655</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,664</t>
+          <t>24,655</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,664 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,655 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,333</t>
+          <t>10,201</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,333</t>
+          <t>10,201</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,333 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,201 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>60,537</t>
+          <t>59,917</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>-619.899</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,917 ▼. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,917 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76337.04</t>
+          <t>76204.24</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76337.04</t>
+          <t>76204.24</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76337.04 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76204.24 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2289.71</t>
+          <t>2285.28</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2289.71</t>
+          <t>2285.28</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1891,19 +1891,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2289.71 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2285.28 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-28 22:30 UTC</t>
+          <t>2026-04-29 15:22 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2133,13 +2133,13 @@
         <v>3.78</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="E2" s="25" t="n">
         <v>4.94</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2167,46 +2167,46 @@
         <v>81</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7138.7998</v>
+        <v>7131.1099</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49141.9297</v>
+        <v>48864.6094</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24663.7988</v>
+        <v>24654.9141</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10332.79</v>
+        <v>10201.46</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59917.46</v>
+        <v>59917.4609</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>17.83</v>
+        <v>18.2</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>99.36</v>
+        <v>105.31</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>103.9</v>
+        <v>109.83</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4610.6001</v>
+        <v>4550.7998</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.978</v>
+        <v>5.947</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.595</v>
+        <v>98.806</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>76337.03909999999</v>
+        <v>76204.24219999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2289.71</v>
+        <v>2285.28</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,6 +72,11 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF4D4D"/>
@@ -87,11 +92,6 @@
       <b val="1"/>
       <color rgb="0000E676"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -181,22 +181,16 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,13 +199,19 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-29 15:22 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-29 22:29 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +709,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.84%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.78%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.78%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
+          <t>+0.060</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▬</t>
+          <t>▲</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.78% ▬ (+0bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.84% ▲ (+6bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.31%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.040</t>
+          <t>+0.010</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -769,14 +769,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.35% ▬ (+4bps). Yield within recent range.</t>
+          <t>10Y yield at 4.36% ▬ (+1bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -798,27 +798,27 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.030</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.94% ▬ (+3bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.94% ▬ (+0bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.52%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.57%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.050</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>BULLISH</t>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.52% ▼. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.50% ▼. Flat curve; economic uncertainty persists.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>+6000.000</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1065,12 +1065,12 @@
           <t>-3.300</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1161,7 +1161,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,12 +1198,12 @@
           <t>-0.083</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$105.31</t>
+          <t>$108.01</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$105.31</t>
+          <t>$108.01</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1240,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $105.31 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $108.01 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$109.83</t>
+          <t>$111.60</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$109.83</t>
+          <t>$111.60</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $109.83 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $111.60 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,550.80</t>
+          <t>$4,561.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,550.80</t>
+          <t>$4,561.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,551 ▬ (-3.8% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,561 ▬ (-3.6% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.947</t>
+          <t>$5.933</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.947 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.933 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1457,12 +1457,12 @@
           <t>+1.000</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.20</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.20</t>
+          <t>18.81</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.20 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 18.81 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.81</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.81</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.81 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.97 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,131</t>
+          <t>7,136</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,131</t>
+          <t>7,136</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,131 ▬. Above 50-day SMA (6,808) — uptrend intact. -0.6% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,136 ▬. Above 50-day SMA (6,808) — uptrend intact. -0.5% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,865</t>
+          <t>48,862</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,865</t>
+          <t>48,862</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,865 ▬.</t>
+          <t>Dow Jones at 48,862 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,655</t>
+          <t>24,673</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,655</t>
+          <t>24,673</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,655 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,673 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,201</t>
+          <t>10,213</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,201</t>
+          <t>10,213</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,201 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,213 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1805,7 +1805,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76204.24</t>
+          <t>75812.02</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76204.24</t>
+          <t>75812.02</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76204.24 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 75812.02 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2285.28</t>
+          <t>2251.43</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2285.28</t>
+          <t>2251.43</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1891,19 +1891,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2285.28 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2251.43 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,23 +2123,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-29 15:22 UTC</t>
+          <t>2026-04-29 22:29 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="E2" s="25" t="n">
         <v>4.94</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2170,43 +2170,43 @@
         <v>285</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7131.1099</v>
+        <v>7135.9502</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48864.6094</v>
+        <v>48861.8086</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24654.9141</v>
+        <v>24673.2402</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10201.46</v>
+        <v>10213.1104</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>59917.4609</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.2</v>
+        <v>18.81</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>105.31</v>
+        <v>108.01</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>109.83</v>
+        <v>111.6</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4550.7998</v>
+        <v>4561</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.947</v>
+        <v>5.933</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.806</v>
+        <v>98.97499999999999</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>76204.24219999999</v>
+        <v>75812.02340000001</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2285.28</v>
+        <v>2251.4299</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -196,6 +196,9 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -209,9 +212,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-29 22:29 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-30 15:17 UTC</t>
         </is>
       </c>
     </row>
@@ -926,32 +926,32 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>214K</t>
+          <t>189K</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>+6000.000</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
+          <t>-26000.000</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Initial claims at 214K ▲. Sub-220K — historically tight labor market.</t>
+          <t>Initial claims at 189K ▼. Sub-220K — historically tight labor market.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1028,7 +1028,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1070,7 +1070,7 @@
           <t>▼</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1156,12 +1156,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1185,32 +1185,32 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>-0.083</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+          <t>+0.201</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Core PCE at 3.0% YoY ▼. Fed's preferred gauge above target — limits easing.</t>
+          <t>Core PCE at 3.2% YoY ▲. Fed's preferred gauge above target — limits easing.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$108.01</t>
+          <t>$106.28</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$108.01</t>
+          <t>$106.28</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $108.01 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $106.28 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$111.60</t>
+          <t>$110.77</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$111.60</t>
+          <t>$110.77</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $111.60 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $110.77 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,561.00</t>
+          <t>$4,629.30</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,561.00</t>
+          <t>$4,629.30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1329,14 +1329,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,561 ▬ (-3.6% wk). Sharp weekly drop — forced liquidation or dollar strength.</t>
+          <t>Gold at $4,629 ▬ (-1.6% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.933</t>
+          <t>$5.958</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.933 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.958 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>282bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>285bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>284bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>+1.000</t>
+          <t>-3.000</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -1462,14 +1462,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 285bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 282bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 18.81 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 17.39 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>98.19</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>98.19</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1546,14 +1546,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.97 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.19 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,136</t>
+          <t>7,166</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,136</t>
+          <t>7,166</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,136 ▬. Above 50-day SMA (6,808) — uptrend intact. -0.5% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,166 ▬. Above 50-day SMA (6,814) — uptrend intact. -0.1% from 52-week high.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>48,862</t>
+          <t>49,390</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>48,862</t>
+          <t>49,390</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1679,14 +1679,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 48,862 ▬.</t>
+          <t>Dow Jones at 49,390 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,673</t>
+          <t>24,723</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,673</t>
+          <t>24,723</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,673 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,723 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,213</t>
+          <t>10,371</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,213</t>
+          <t>10,371</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1763,14 +1763,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,213 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,371 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,32 +1787,32 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>59,285</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>59,917</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>59,917</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
+          <t>-632.541</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,917 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,285 ▼. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>75812.02</t>
+          <t>76350.83</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>75812.02</t>
+          <t>76350.83</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 75812.02 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76350.83 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2251.43</t>
+          <t>2263.36</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2251.43</t>
+          <t>2263.36</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2251.43 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2263.36 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-29 22:29 UTC</t>
+          <t>2026-04-30 15:17 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2148,13 +2148,13 @@
         <v>2.6731</v>
       </c>
       <c r="I2" s="25" t="n">
-        <v>2.9678</v>
+        <v>3.2028</v>
       </c>
       <c r="J2" s="25" t="n">
         <v>4.3</v>
       </c>
       <c r="K2" s="25" t="n">
-        <v>214000</v>
+        <v>189000</v>
       </c>
       <c r="L2" s="25" t="n">
         <v>178</v>
@@ -2167,46 +2167,46 @@
         <v>81</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7135.9502</v>
+        <v>7165.7798</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>48861.8086</v>
+        <v>49389.7891</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24673.2402</v>
+        <v>24723.0977</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10213.1104</v>
+        <v>10371.4102</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59917.4609</v>
+        <v>59284.92</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>18.81</v>
+        <v>17.39</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>108.01</v>
+        <v>106.28</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>111.6</v>
+        <v>110.77</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4561</v>
+        <v>4629.2998</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.933</v>
+        <v>5.958</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.97499999999999</v>
+        <v>98.194</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>75812.02340000001</v>
+        <v>76350.8281</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2251.4299</v>
+        <v>2263.3601</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -83,15 +83,15 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="0000E676"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000E676"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -190,28 +190,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-30 15:17 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-04-30 22:27 UTC</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.84%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.78%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.060</t>
+          <t>+0.080</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.84% ▲ (+6bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.92% ▲ (+8bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,32 +751,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.42%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.36%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.35%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.010</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.060</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.36% ▬ (+1bps). Yield within recent range.</t>
+          <t>10Y yield at 4.42% ▲ (+6bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -793,20 +793,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
+          <t>4.98%</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>4.94%</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>4.94%</t>
-        </is>
-      </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
+          <t>+0.040</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -818,7 +818,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.94% ▬ (+0bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.98% ▬ (+4bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +835,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.50%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>-0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.020</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.50% ▼. Flat curve; economic uncertainty persists.</t>
+          <t>2s10s spread at 0.52% ▲. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +897,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +939,12 @@
           <t>-26000.000</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +981,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1065,12 +1065,12 @@
           <t>-3.300</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,12 +1114,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1156,12 +1156,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,12 +1198,12 @@
           <t>+0.201</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$106.28</t>
+          <t>$105.44</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$106.28</t>
+          <t>$105.44</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,7 +1240,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $106.28 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $105.44 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$110.77</t>
+          <t>$111.22</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$110.77</t>
+          <t>$111.22</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1287,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $110.77 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $111.22 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,629.30</t>
+          <t>$4,643.70</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,629.30</t>
+          <t>$4,643.70</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1324,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,629 ▬ (-1.6% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,644 ▬ (-1.3% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.958</t>
+          <t>$6.031</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1371,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.958 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $6.031 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1420,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1457,12 +1457,12 @@
           <t>-3.000</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 17.39 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 16.89 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.19</t>
+          <t>98.09</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.19</t>
+          <t>98.09</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1541,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.19 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.09 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,166</t>
+          <t>7,209</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,166</t>
+          <t>7,209</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1637,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,166 ▬. Above 50-day SMA (6,814) — uptrend intact. -0.1% from 52-week high.</t>
+          <t>S&amp;P 500 at 7,209 ▬. Above 50-day SMA (6,815) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,390</t>
+          <t>49,652</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,390</t>
+          <t>49,652</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1674,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,390 ▬.</t>
+          <t>Dow Jones at 49,652 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,723</t>
+          <t>24,892</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,723</t>
+          <t>24,892</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1721,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,723 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 24,892 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,371</t>
+          <t>10,379</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,371</t>
+          <t>10,379</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1758,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,371 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,379 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1800,12 +1800,12 @@
           <t>-632.541</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76350.83</t>
+          <t>76390.98</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76350.83</t>
+          <t>76390.98</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1854,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76350.83 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 76390.98 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2263.36</t>
+          <t>2259.90</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2263.36</t>
+          <t>2259.90</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1891,7 +1891,7 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2263.36 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2259.90 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,23 +2123,23 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-30 15:17 UTC</t>
+          <t>2026-04-30 22:27 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
         <v>3.75</v>
       </c>
       <c r="C2" s="25" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="D2" s="25" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="E2" s="25" t="n">
-        <v>4.94</v>
+        <v>4.98</v>
       </c>
       <c r="F2" s="25" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>3.3202</v>
@@ -2170,43 +2170,43 @@
         <v>282</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7165.7798</v>
+        <v>7209.0098</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49389.7891</v>
+        <v>49652.1406</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24723.0977</v>
+        <v>24892.3125</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10371.4102</v>
+        <v>10378.8203</v>
       </c>
       <c r="U2" s="25" t="n">
         <v>59284.92</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>17.39</v>
+        <v>16.89</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>106.28</v>
+        <v>105.44</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>110.77</v>
+        <v>111.22</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4629.2998</v>
+        <v>4643.7002</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>5.958</v>
+        <v>6.0315</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.194</v>
+        <v>98.09099999999999</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>76350.8281</v>
+        <v>76390.97659999999</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2263.3601</v>
+        <v>2259.8999</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -606,7 +606,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-04-30 22:27 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-05-01 14:19 UTC</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$105.44</t>
+          <t>$100.58</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$105.44</t>
+          <t>$100.58</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $105.44 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $100.58 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$111.22</t>
+          <t>$107.76</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$111.22</t>
+          <t>$107.76</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $111.22 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $107.76 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,643.70</t>
+          <t>$4,646.00</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,643.70</t>
+          <t>$4,646.00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,644 ▬ (-1.3% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,646 ▬ (-1.6% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$6.031</t>
+          <t>$5.996</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $6.031 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.996 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
+          <t>283bps</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
           <t>282bps</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>285bps</t>
-        </is>
-      </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>-3.000</t>
+          <t>+1.000</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>HY spread at 282bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
+          <t>HY spread at 283bps ▬. Below 300bps — compressed; complacency or strong growth.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 16.89 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 16.58 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>98.09</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>98.09</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 98.09 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 97.78 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,209</t>
+          <t>7,267</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,209</t>
+          <t>7,267</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,209 ▬. Above 50-day SMA (6,815) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,267 ▬. Above 50-day SMA (6,823) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,652</t>
+          <t>49,965</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,652</t>
+          <t>49,965</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,652 ▬.</t>
+          <t>Dow Jones at 49,965 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>24,892</t>
+          <t>25,168</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>24,892</t>
+          <t>25,168</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 24,892 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 25,168 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,379</t>
+          <t>10,354</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,379</t>
+          <t>10,354</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,379 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,354 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>59,285</t>
+          <t>59,513</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,917</t>
+          <t>59,513</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>-632.541</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>▼</t>
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,285 ▼. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,513 ▬. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>76390.98</t>
+          <t>78492.00</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>76390.98</t>
+          <t>78492.00</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 76390.98 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78492.00 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2259.90</t>
+          <t>2314.43</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2259.90</t>
+          <t>2314.43</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2259.90 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2314.43 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>2026-04-30 22:27 UTC</t>
+          <t>2026-05-01 14:19 UTC</t>
         </is>
       </c>
       <c r="B2" s="25" t="n">
@@ -2167,46 +2167,46 @@
         <v>81</v>
       </c>
       <c r="P2" s="25" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q2" s="25" t="n">
-        <v>7209.0098</v>
+        <v>7267.1802</v>
       </c>
       <c r="R2" s="25" t="n">
-        <v>49652.1406</v>
+        <v>49965.0117</v>
       </c>
       <c r="S2" s="25" t="n">
-        <v>24892.3125</v>
+        <v>25167.7383</v>
       </c>
       <c r="T2" s="25" t="n">
-        <v>10378.8203</v>
+        <v>10354.0703</v>
       </c>
       <c r="U2" s="25" t="n">
-        <v>59284.92</v>
+        <v>59513.1211</v>
       </c>
       <c r="V2" s="25" t="n">
-        <v>16.89</v>
+        <v>16.58</v>
       </c>
       <c r="W2" s="25" t="n">
-        <v>105.44</v>
+        <v>100.58</v>
       </c>
       <c r="X2" s="25" t="n">
-        <v>111.22</v>
+        <v>107.76</v>
       </c>
       <c r="Y2" s="25" t="n">
-        <v>4643.7002</v>
+        <v>4646</v>
       </c>
       <c r="Z2" s="25" t="n">
-        <v>6.0315</v>
+        <v>5.9955</v>
       </c>
       <c r="AA2" s="25" t="n">
-        <v>98.09099999999999</v>
+        <v>97.783</v>
       </c>
       <c r="AB2" s="25" t="n">
-        <v>76390.97659999999</v>
+        <v>78492</v>
       </c>
       <c r="AC2" s="25" t="n">
-        <v>2259.8999</v>
+        <v>2314.4299</v>
       </c>
       <c r="AD2" s="25" t="n"/>
     </row>

--- a/macro_pulse.xlsx
+++ b/macro_pulse.xlsx
@@ -72,9 +72,10 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-      <sz val="10"/>
+      <color rgb="0000E676"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -83,14 +84,13 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0000E676"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FF4D4D"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -181,37 +181,34 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -606,7 +603,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ MACRO PULSE  |  2026-05-01 14:19 UTC</t>
+          <t>⚡ MACRO PULSE  |  2026-05-01 22:11 UTC</t>
         </is>
       </c>
     </row>
@@ -709,32 +706,32 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
+          <t>3.88%</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
           <t>3.92%</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>3.84%</t>
-        </is>
-      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>+0.080</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>▲</t>
+          <t>▬</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2Y yield at 3.92% ▲ (+8bps). Reflecting current rate expectations.</t>
+          <t>2Y yield at 3.88% ▬ (-4bps). Reflecting current rate expectations.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -751,32 +748,32 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>4.40%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>4.42%</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>4.36%</t>
-        </is>
-      </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>+0.060</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>BEARISH</t>
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10Y yield at 4.42% ▲ (+6bps). Yield within recent range.</t>
+          <t>10Y yield at 4.40% ▬ (-2bps). Yield within recent range.</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -798,27 +795,27 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.98%</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>+0.040</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+          <t>+0.000</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>30Y yield at 4.98% ▬ (+4bps). Long-end elevated; term premium rising.</t>
+          <t>30Y yield at 4.98% ▬ (+0bps). Long-end elevated; term premium rising.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -835,32 +832,32 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>0.52%</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>+0.020</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>▬</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2s10s spread at 0.52% ▲. Curve steepening — growth optimism or reflation trade.</t>
+          <t>2s10s spread at 0.51% ▬. Curve steepening — growth optimism or reflation trade.</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -897,7 +894,7 @@
           <t>-0.100</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -939,12 +936,12 @@
           <t>-26000.000</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -981,12 +978,12 @@
           <t>+311.000</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1023,12 +1020,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1065,12 +1062,12 @@
           <t>-3.300</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1114,12 +1111,12 @@
           <t>+0.656</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1156,12 +1153,12 @@
           <t>-0.060</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
@@ -1198,12 +1195,12 @@
           <t>+0.201</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
@@ -1227,12 +1224,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>$100.58</t>
+          <t>$102.50</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>$100.58</t>
+          <t>$102.50</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1240,19 +1237,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>WTI at $100.58 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
+          <t>WTI at $102.50 ▬. Triple digits — supply shock; stagflation risk elevated.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1269,12 +1266,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>$107.76</t>
+          <t>$108.83</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>$107.76</t>
+          <t>$108.83</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1287,14 +1284,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Brent at $107.76 ▬. Global crude benchmark tracking geopolitical risk.</t>
+          <t>Brent at $108.83 ▬. Global crude benchmark tracking geopolitical risk.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1311,12 +1308,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>$4,646.00</t>
+          <t>$4,625.60</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>$4,646.00</t>
+          <t>$4,625.60</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1324,19 +1321,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Gold at $4,646 ▬ (-1.6% wk). All-time high territory — persistent safe-haven demand.</t>
+          <t>Gold at $4,626 ▬ (-2.0% wk). All-time high territory — persistent safe-haven demand.</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -1353,12 +1350,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>$5.996</t>
+          <t>$5.964</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1371,14 +1368,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Copper at $5.996 ▬. Above $4 — strong global growth signal.</t>
+          <t>Copper at $5.964 ▬. Above $4 — strong global growth signal.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1420,7 +1417,7 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1457,12 +1454,12 @@
           <t>+1.000</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
@@ -1486,12 +1483,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1511,7 +1508,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>VIX at 16.58 ▬. Moderate concern; market in transition.</t>
+          <t>VIX at 16.99 ▬. Moderate concern; market in transition.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -1528,12 +1525,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>98.21</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>98.21</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1541,19 +1538,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>DXY at 97.78 ▬. Weak dollar — supports commodities and overseas earnings.</t>
+          <t>DXY at 98.21 ▬. Weak dollar — supports commodities and overseas earnings.</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -1619,12 +1616,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>7,267</t>
+          <t>7,230</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>7,267</t>
+          <t>7,230</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1637,14 +1634,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>S&amp;P 500 at 7,267 ▬. Above 50-day SMA (6,823) — uptrend intact.</t>
+          <t>S&amp;P 500 at 7,230 ▬. Above 50-day SMA (6,822) — uptrend intact.</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1661,12 +1658,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>49,965</t>
+          <t>49,499</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>49,965</t>
+          <t>49,499</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1674,19 +1671,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Dow Jones at 49,965 ▬.</t>
+          <t>Dow Jones at 49,499 ▬.</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -1703,12 +1700,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>25,168</t>
+          <t>25,114</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>25,168</t>
+          <t>25,114</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1721,14 +1718,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Nasdaq at 25,168 ▬. Tech complex tracking broader risk tone.</t>
+          <t>Nasdaq at 25,114 ▬. Tech complex tracking broader risk tone.</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1745,12 +1742,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>10,354</t>
+          <t>10,364</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>10,354</t>
+          <t>10,364</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1758,19 +1755,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>FTSE 100 at 10,354 ▬. UK equities reflecting global risk sentiment.</t>
+          <t>FTSE 100 at 10,364 ▬. UK equities reflecting global risk sentiment.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -1792,27 +1789,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59,513</t>
+          <t>59,285</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>+0.000</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>▬</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
+          <t>+228.198</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>BULLISH</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Nikkei at 59,513 ▬. JPY dynamics and global tech flows key drivers.</t>
+          <t>Nikkei at 59,513 ▲. JPY dynamics and global tech flows key drivers.</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1836,12 +1833,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>78492.00</t>
+          <t>78286.14</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>78492.00</t>
+          <t>78286.14</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1854,14 +1851,14 @@
           <t>▬</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Bitcoin at 78492.00 ▬. Signal: BEARISH.</t>
+          <t>Bitcoin at 78286.14 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1878,12 +1875,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>2314.43</t>
+          <t>2295.70</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2314.43</t>
+          <t>2295.70</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -1891,19 +1888,19 @@
           <t>+0.000</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>▬</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Ethereum at 2314.43 ▬. Signal: BEARISH.</t>
+          <t>Ethereum at 2295.70 ▬. Signal: BEARISH.</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -2121,94 +2118,94 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>2026-05-01 14:19 UTC</t>
-        </is>
-      </c>
-      <c r="B2" s="25" t="n">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:11 UTC</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="n">
         <v>3.75</v>
       </c>
-      <c r="C2" s="25" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="D2" s="25" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E2" s="25" t="n">
+      <c r="C2" s="24" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="D2" s="24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E2" s="24" t="n">
         <v>4.98</v>
       </c>
-      <c r="F2" s="25" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G2" s="25" t="n">
+      <c r="F2" s="24" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G2" s="24" t="n">
         <v>3.3202</v>
       </c>
-      <c r="H2" s="25" t="n">
+      <c r="H2" s="24" t="n">
         <v>2.6731</v>
       </c>
-      <c r="I2" s="25" t="n">
+      <c r="I2" s="24" t="n">
         <v>3.2028</v>
       </c>
-      <c r="J2" s="25" t="n">
+      <c r="J2" s="24" t="n">
         <v>4.3</v>
       </c>
-      <c r="K2" s="25" t="n">
+      <c r="K2" s="24" t="n">
         <v>189000</v>
       </c>
-      <c r="L2" s="25" t="n">
+      <c r="L2" s="24" t="n">
         <v>178</v>
       </c>
-      <c r="M2" s="25" t="n"/>
-      <c r="N2" s="25" t="n">
+      <c r="M2" s="24" t="n"/>
+      <c r="N2" s="24" t="n">
         <v>53.3</v>
       </c>
-      <c r="O2" s="25" t="n">
+      <c r="O2" s="24" t="n">
         <v>81</v>
       </c>
-      <c r="P2" s="25" t="n">
+      <c r="P2" s="24" t="n">
         <v>283</v>
       </c>
-      <c r="Q2" s="25" t="n">
-        <v>7267.1802</v>
-      </c>
-      <c r="R2" s="25" t="n">
-        <v>49965.0117</v>
-      </c>
-      <c r="S2" s="25" t="n">
-        <v>25167.7383</v>
-      </c>
-      <c r="T2" s="25" t="n">
-        <v>10354.0703</v>
-      </c>
-      <c r="U2" s="25" t="n">
-        <v>59513.1211</v>
-      </c>
-      <c r="V2" s="25" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="W2" s="25" t="n">
-        <v>100.58</v>
-      </c>
-      <c r="X2" s="25" t="n">
-        <v>107.76</v>
-      </c>
-      <c r="Y2" s="25" t="n">
-        <v>4646</v>
-      </c>
-      <c r="Z2" s="25" t="n">
-        <v>5.9955</v>
-      </c>
-      <c r="AA2" s="25" t="n">
-        <v>97.783</v>
-      </c>
-      <c r="AB2" s="25" t="n">
-        <v>78492</v>
-      </c>
-      <c r="AC2" s="25" t="n">
-        <v>2314.4299</v>
-      </c>
-      <c r="AD2" s="25" t="n"/>
+      <c r="Q2" s="24" t="n">
+        <v>7230.1201</v>
+      </c>
+      <c r="R2" s="24" t="n">
+        <v>49499.2695</v>
+      </c>
+      <c r="S2" s="24" t="n">
+        <v>25114.4434</v>
+      </c>
+      <c r="T2" s="24" t="n">
+        <v>10363.9297</v>
+      </c>
+      <c r="U2" s="24" t="n">
+        <v>59513.12</v>
+      </c>
+      <c r="V2" s="24" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="W2" s="24" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="X2" s="24" t="n">
+        <v>108.83</v>
+      </c>
+      <c r="Y2" s="24" t="n">
+        <v>4625.6001</v>
+      </c>
+      <c r="Z2" s="24" t="n">
+        <v>5.9645</v>
+      </c>
+      <c r="AA2" s="24" t="n">
+        <v>98.211</v>
+      </c>
+      <c r="AB2" s="24" t="n">
+        <v>78286.1406</v>
+      </c>
+      <c r="AC2" s="24" t="n">
+        <v>2295.7</v>
+      </c>
+      <c r="AD2" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2277,7 +2274,7 @@
           <t>FED_FUNDS</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Fed Funds Rate</t>
         </is>
@@ -2314,7 +2311,7 @@
           <t>US_2Y</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>US 2Y Treasury</t>
         </is>
@@ -2351,7 +2348,7 @@
           <t>US_10Y</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>US 10Y Treasury</t>
         </is>
@@ -2388,7 +2385,7 @@
           <t>US_30Y</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>US 30Y Treasury</t>
         </is>
@@ -2425,7 +2422,7 @@
           <t>SPREAD_2S10S</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>2s10s Yield Spread</t>
         </is>
@@ -2462,7 +2459,7 @@
           <t>CPI_YOY</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>CPI YoY</t>
         </is>
@@ -2499,7 +2496,7 @@
           <t>CORE_CPI_YOY</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Core CPI YoY</t>
         </is>
@@ -2536,7 +2533,7 @@
           <t>CORE_PCE_YOY</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Core PCE YoY</t>
         </is>
@@ -2573,7 +2570,7 @@
           <t>UNEMPLOYMENT</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Unemployment Rate</t>
         </is>
@@ -2610,7 +2607,7 @@
           <t>INITIAL_CLAIMS</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Initial Jobless Claims</t>
         </is>
@@ -2647,7 +2644,7 @@
           <t>NFP</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Nonfarm Payrolls MoM</t>
         </is>
@@ -2684,7 +2681,7 @@
           <t>ISM_MFG</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>ISM Manufacturing PMI</t>
         </is>
@@ -2721,7 +2718,7 @@
           <t>CONSUMER_CONF</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Consumer Confidence (Mich)</t>
         </is>
@@ -2758,7 +2755,7 @@
           <t>IG_SPREAD</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>IG Credit Spread</t>
         </is>
@@ -2795,7 +2792,7 @@
           <t>HY_SPREAD</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>HY Credit Spread</t>
         </is>
@@ -2832,7 +2829,7 @@
           <t>VIX</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>VIX</t>
         </is>
@@ -2869,7 +2866,7 @@
           <t>SP500</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
@@ -2906,7 +2903,7 @@
           <t>DOW</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Dow Jones</t>
         </is>
@@ -2943,7 +2940,7 @@
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Nasdaq Composite</t>
         </is>
@@ -2980,7 +2977,7 @@
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>FTSE 100</t>
         </is>
@@ -3017,7 +3014,7 @@
           <t>NIKKEI</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Nikkei 225</t>
         </is>
@@ -3054,7 +3051,7 @@
           <t>OIL_WTI</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>WTI Crude Oil</t>
         </is>
@@ -3091,7 +3088,7 @@
           <t>OIL_BRT</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Brent Crude Oil</t>
         </is>
@@ -3128,7 +3125,7 @@
           <t>GOLD</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
@@ -3165,7 +3162,7 @@
           <t>COPPER</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Copper</t>
         </is>
@@ -3202,7 +3199,7 @@
           <t>DXY</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>DXY Dollar Index</t>
         </is>
@@ -3239,7 +3236,7 @@
           <t>PUT_CALL</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Put/Call Ratio</t>
         </is>
